--- a/SoRoSim Robots/my_robot(2.0to1.0)/Validation(2.0to1.0)(correct).xlsx
+++ b/SoRoSim Robots/my_robot(2.0to1.0)/Validation(2.0to1.0)(correct).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/SoRoSim Robots/my_robot(2.0to1.0)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="843" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F81C1F4D-4A69-48D0-A781-8E98083D757A}"/>
+  <xr:revisionPtr revIDLastSave="858" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADEA899C-E081-4095-8226-081B2CD6ECF1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
@@ -39,8 +39,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
   <si>
     <t>Fx (N)</t>
   </si>
@@ -141,6 +163,9 @@
   <si>
     <t>`</t>
   </si>
+  <si>
+    <t>Abs Mean error</t>
+  </si>
 </sst>
 </file>
 
@@ -148,7 +173,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -482,20 +507,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -510,36 +565,15 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -555,26 +589,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3109,172 +3132,172 @@
   <dimension ref="A1:AJ52"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="26" width="9.28515625" style="4" customWidth="1"/>
-    <col min="27" max="27" width="8" style="4"/>
-    <col min="28" max="34" width="15.28515625" style="4" customWidth="1"/>
-    <col min="35" max="16384" width="8" style="4"/>
+    <col min="1" max="26" width="9.28515625" style="3" customWidth="1"/>
+    <col min="27" max="27" width="8" style="3"/>
+    <col min="28" max="34" width="15.28515625" style="3" customWidth="1"/>
+    <col min="35" max="16384" width="8" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
+      <c r="A1" s="27"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="7" t="s">
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="9" t="s">
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="13" t="s">
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="AC2" s="14"/>
-      <c r="AD2" s="14"/>
-      <c r="AE2" s="14"/>
-      <c r="AF2" s="14"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="12"/>
-      <c r="AI2" s="16"/>
-      <c r="AJ2" s="16"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="30"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="K3" s="17" t="s">
+      <c r="J3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="17" t="s">
+      <c r="L3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="19" t="s">
+      <c r="M3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="20" t="s">
+      <c r="N3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="O3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="P3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="Q3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="R3" s="17" t="s">
+      <c r="Q3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="17" t="s">
+      <c r="S3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="T3" s="19" t="s">
+      <c r="T3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="U3" s="21"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="21"/>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="21"/>
-      <c r="Z3" s="21"/>
-      <c r="AA3" s="12"/>
-      <c r="AB3" s="20" t="s">
+      <c r="U3" s="11"/>
+      <c r="V3" s="11"/>
+      <c r="W3" s="11"/>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11"/>
+      <c r="Z3" s="11"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="AC3" s="17" t="s">
+      <c r="AC3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="AD3" s="17" t="s">
+      <c r="AD3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AE3" s="17" t="s">
+      <c r="AE3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AF3" s="17" t="s">
+      <c r="AF3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AG3" s="22" t="s">
+      <c r="AG3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="AI3" s="12"/>
-      <c r="AJ3" s="12"/>
+      <c r="AI3" s="5"/>
+      <c r="AJ3" s="5"/>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -3337,44 +3360,44 @@
       <c r="T4" s="1">
         <v>-0.311</v>
       </c>
-      <c r="U4" s="23">
+      <c r="U4" s="13">
         <f>ABS(G4-N4)</f>
         <v>6.2803874972681994E-4</v>
       </c>
-      <c r="V4" s="23">
+      <c r="V4" s="13">
         <f t="shared" ref="V4:Z4" si="0">ABS(H4-O4)</f>
         <v>1.1786323321519401E-3</v>
       </c>
-      <c r="W4" s="23">
+      <c r="W4" s="13">
         <f t="shared" si="0"/>
         <v>1.4774313874755599E-3</v>
       </c>
-      <c r="X4" s="23">
+      <c r="X4" s="13">
         <f t="shared" si="0"/>
         <v>1.0007000908068997E-2</v>
       </c>
-      <c r="Y4" s="23">
+      <c r="Y4" s="13">
         <f t="shared" si="0"/>
         <v>1.5940533662171991E-2</v>
       </c>
-      <c r="Z4" s="23">
+      <c r="Z4" s="13">
         <f t="shared" si="0"/>
         <v>6.0481913180748005E-3</v>
       </c>
-      <c r="AB4" s="24" t="s">
+      <c r="AB4" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="AC4" s="25" t="s">
+      <c r="AC4" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="AD4" s="25" t="s">
+      <c r="AD4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="AE4" s="17"/>
-      <c r="AF4" s="25" t="s">
+      <c r="AE4" s="7"/>
+      <c r="AF4" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="AG4" s="26" t="s">
+      <c r="AG4" s="16" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3439,51 +3462,51 @@
       <c r="T5" s="1">
         <v>-0.378</v>
       </c>
-      <c r="U5" s="23">
+      <c r="U5" s="13">
         <f t="shared" ref="U5:U23" si="1">ABS(G5-N5)</f>
         <v>9.24892540965939E-4</v>
       </c>
-      <c r="V5" s="23">
+      <c r="V5" s="13">
         <f t="shared" ref="V5:V23" si="2">ABS(H5-O5)</f>
         <v>9.53616969056916E-4</v>
       </c>
-      <c r="W5" s="23">
+      <c r="W5" s="13">
         <f t="shared" ref="W5:W23" si="3">ABS(I5-P5)</f>
         <v>7.3689085566409906E-4</v>
       </c>
-      <c r="X5" s="23">
+      <c r="X5" s="13">
         <f t="shared" ref="X5:X23" si="4">ABS(J5-Q5)</f>
         <v>3.3868887557654048E-2</v>
       </c>
-      <c r="Y5" s="23">
+      <c r="Y5" s="13">
         <f t="shared" ref="Y5:Y23" si="5">ABS(K5-R5)</f>
         <v>4.5176100334453961E-2</v>
       </c>
-      <c r="Z5" s="23">
+      <c r="Z5" s="13">
         <f t="shared" ref="Z5:Z23" si="6">ABS(L5-S5)</f>
         <v>1.4194562075134302E-2</v>
       </c>
-      <c r="AB5" s="27">
+      <c r="AB5" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G2</f>
         <v>0</v>
       </c>
-      <c r="AC5" s="27">
+      <c r="AC5" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F2</f>
         <v>0</v>
       </c>
-      <c r="AD5" s="27">
+      <c r="AD5" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E2</f>
         <v>0</v>
       </c>
-      <c r="AE5" s="27">
+      <c r="AE5" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D2</f>
         <v>0</v>
       </c>
-      <c r="AF5" s="27">
+      <c r="AF5" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C2</f>
         <v>0</v>
       </c>
-      <c r="AG5" s="27">
+      <c r="AG5" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B2</f>
         <v>0</v>
       </c>
@@ -3549,51 +3572,51 @@
       <c r="T6" s="1">
         <v>-0.502</v>
       </c>
-      <c r="U6" s="23">
+      <c r="U6" s="13">
         <f t="shared" si="1"/>
         <v>1.9244685726215801E-3</v>
       </c>
-      <c r="V6" s="23">
+      <c r="V6" s="13">
         <f t="shared" si="2"/>
         <v>3.5915794253648299E-3</v>
       </c>
-      <c r="W6" s="23">
+      <c r="W6" s="13">
         <f t="shared" si="3"/>
         <v>5.4185841191651991E-3</v>
       </c>
-      <c r="X6" s="23">
+      <c r="X6" s="13">
         <f t="shared" si="4"/>
         <v>8.8098169559009204E-2</v>
       </c>
-      <c r="Y6" s="23">
+      <c r="Y6" s="13">
         <f t="shared" si="5"/>
         <v>3.6976907784850965E-2</v>
       </c>
-      <c r="Z6" s="23">
+      <c r="Z6" s="13">
         <f t="shared" si="6"/>
         <v>3.0547186358636503E-2</v>
       </c>
-      <c r="AB6" s="27">
+      <c r="AB6" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G3</f>
         <v>0</v>
       </c>
-      <c r="AC6" s="27">
+      <c r="AC6" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F3</f>
         <v>0</v>
       </c>
-      <c r="AD6" s="27">
+      <c r="AD6" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E3</f>
         <v>0</v>
       </c>
-      <c r="AE6" s="27">
+      <c r="AE6" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D3</f>
         <v>0</v>
       </c>
-      <c r="AF6" s="27">
+      <c r="AF6" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C3</f>
         <v>0</v>
       </c>
-      <c r="AG6" s="27">
+      <c r="AG6" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B3</f>
         <v>0</v>
       </c>
@@ -3659,51 +3682,51 @@
       <c r="T7" s="1">
         <v>-0.17799999999999999</v>
       </c>
-      <c r="U7" s="23">
+      <c r="U7" s="13">
         <f t="shared" si="1"/>
         <v>2.9160777304359099E-4</v>
       </c>
-      <c r="V7" s="23">
+      <c r="V7" s="13">
         <f t="shared" si="2"/>
         <v>1.9303452979865102E-4</v>
       </c>
-      <c r="W7" s="23">
+      <c r="W7" s="13">
         <f t="shared" si="3"/>
         <v>3.641361998115997E-4</v>
       </c>
-      <c r="X7" s="23">
+      <c r="X7" s="13">
         <f t="shared" si="4"/>
         <v>3.127958188983801E-2</v>
       </c>
-      <c r="Y7" s="23">
+      <c r="Y7" s="13">
         <f t="shared" si="5"/>
         <v>8.5145783674969999E-3</v>
       </c>
-      <c r="Z7" s="23">
+      <c r="Z7" s="13">
         <f t="shared" si="6"/>
         <v>5.0157873606571195E-3</v>
       </c>
-      <c r="AB7" s="27">
+      <c r="AB7" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G4</f>
         <v>0</v>
       </c>
-      <c r="AC7" s="27">
+      <c r="AC7" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F4</f>
         <v>0</v>
       </c>
-      <c r="AD7" s="27">
+      <c r="AD7" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E4</f>
         <v>0</v>
       </c>
-      <c r="AE7" s="27">
+      <c r="AE7" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D4</f>
         <v>0</v>
       </c>
-      <c r="AF7" s="27">
+      <c r="AF7" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C4</f>
         <v>0</v>
       </c>
-      <c r="AG7" s="27">
+      <c r="AG7" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B4</f>
         <v>0</v>
       </c>
@@ -3769,51 +3792,51 @@
       <c r="T8" s="1">
         <v>-0.43</v>
       </c>
-      <c r="U8" s="23">
+      <c r="U8" s="13">
         <f t="shared" si="1"/>
         <v>7.9737447946100204E-4</v>
       </c>
-      <c r="V8" s="23">
+      <c r="V8" s="13">
         <f t="shared" si="2"/>
         <v>9.3622279784621001E-4</v>
       </c>
-      <c r="W8" s="23">
+      <c r="W8" s="13">
         <f t="shared" si="3"/>
         <v>6.8080105046729872E-4</v>
       </c>
-      <c r="X8" s="23">
+      <c r="X8" s="13">
         <f t="shared" si="4"/>
         <v>3.1598222615108973E-2</v>
       </c>
-      <c r="Y8" s="23">
+      <c r="Y8" s="13">
         <f t="shared" si="5"/>
         <v>1.0862876700522994E-2</v>
       </c>
-      <c r="Z8" s="23">
+      <c r="Z8" s="13">
         <f t="shared" si="6"/>
         <v>1.09848050429718E-2</v>
       </c>
-      <c r="AB8" s="27">
+      <c r="AB8" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G5</f>
         <v>0</v>
       </c>
-      <c r="AC8" s="27">
+      <c r="AC8" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F5</f>
         <v>0</v>
       </c>
-      <c r="AD8" s="27">
+      <c r="AD8" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E5</f>
         <v>0</v>
       </c>
-      <c r="AE8" s="27">
+      <c r="AE8" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D5</f>
         <v>0</v>
       </c>
-      <c r="AF8" s="27">
+      <c r="AF8" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C5</f>
         <v>0</v>
       </c>
-      <c r="AG8" s="27">
+      <c r="AG8" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B5</f>
         <v>0</v>
       </c>
@@ -3879,51 +3902,51 @@
       <c r="T9" s="1">
         <v>-0.76800000000000002</v>
       </c>
-      <c r="U9" s="23">
+      <c r="U9" s="13">
         <f t="shared" si="1"/>
         <v>2.1518003405959097E-3</v>
       </c>
-      <c r="V9" s="23">
+      <c r="V9" s="13">
         <f t="shared" si="2"/>
         <v>2.8571938746291903E-3</v>
       </c>
-      <c r="W9" s="23">
+      <c r="W9" s="13">
         <f t="shared" si="3"/>
         <v>1.5838587053252987E-3</v>
       </c>
-      <c r="X9" s="23">
+      <c r="X9" s="13">
         <f t="shared" si="4"/>
         <v>2.1457480787230976E-2</v>
       </c>
-      <c r="Y9" s="23">
+      <c r="Y9" s="13">
         <f t="shared" si="5"/>
         <v>6.5558638524370993E-2</v>
       </c>
-      <c r="Z9" s="23">
+      <c r="Z9" s="13">
         <f t="shared" si="6"/>
         <v>3.7414305748849498E-2</v>
       </c>
-      <c r="AB9" s="27">
+      <c r="AB9" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G6</f>
         <v>0</v>
       </c>
-      <c r="AC9" s="27">
+      <c r="AC9" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F6</f>
         <v>0</v>
       </c>
-      <c r="AD9" s="27">
+      <c r="AD9" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E6</f>
         <v>0</v>
       </c>
-      <c r="AE9" s="27">
+      <c r="AE9" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D6</f>
         <v>0</v>
       </c>
-      <c r="AF9" s="27">
+      <c r="AF9" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C6</f>
         <v>0</v>
       </c>
-      <c r="AG9" s="27">
+      <c r="AG9" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B6</f>
         <v>0</v>
       </c>
@@ -3989,51 +4012,51 @@
       <c r="T10" s="1">
         <v>-0.497</v>
       </c>
-      <c r="U10" s="23">
+      <c r="U10" s="13">
         <f t="shared" si="1"/>
         <v>9.4238519239925995E-4</v>
       </c>
-      <c r="V10" s="23">
+      <c r="V10" s="13">
         <f t="shared" si="2"/>
         <v>2.7068998135925302E-3</v>
       </c>
-      <c r="W10" s="23">
+      <c r="W10" s="13">
         <f t="shared" si="3"/>
         <v>1.2779286707034002E-3</v>
       </c>
-      <c r="X10" s="23">
+      <c r="X10" s="13">
         <f t="shared" si="4"/>
         <v>2.4737480008978019E-2</v>
       </c>
-      <c r="Y10" s="23">
+      <c r="Y10" s="13">
         <f t="shared" si="5"/>
         <v>5.7335245381880118E-3</v>
       </c>
-      <c r="Z10" s="23">
+      <c r="Z10" s="13">
         <f t="shared" si="6"/>
         <v>1.7506338282292901E-2</v>
       </c>
-      <c r="AB10" s="27">
+      <c r="AB10" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G7</f>
         <v>0</v>
       </c>
-      <c r="AC10" s="27">
+      <c r="AC10" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F7</f>
         <v>0</v>
       </c>
-      <c r="AD10" s="27">
+      <c r="AD10" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E7</f>
         <v>0</v>
       </c>
-      <c r="AE10" s="27">
+      <c r="AE10" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D7</f>
         <v>0</v>
       </c>
-      <c r="AF10" s="27">
+      <c r="AF10" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C7</f>
         <v>0</v>
       </c>
-      <c r="AG10" s="27">
+      <c r="AG10" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B7</f>
         <v>0</v>
       </c>
@@ -4099,51 +4122,51 @@
       <c r="T11" s="1">
         <v>-0.23</v>
       </c>
-      <c r="U11" s="23">
+      <c r="U11" s="13">
         <f t="shared" si="1"/>
         <v>1.80158519705167E-3</v>
       </c>
-      <c r="V11" s="23">
+      <c r="V11" s="13">
         <f t="shared" si="2"/>
         <v>5.2613697387113604E-4</v>
       </c>
-      <c r="W11" s="23">
+      <c r="W11" s="13">
         <f t="shared" si="3"/>
         <v>2.9303173940729843E-4</v>
       </c>
-      <c r="X11" s="23">
+      <c r="X11" s="13">
         <f t="shared" si="4"/>
         <v>3.527852851694302E-2</v>
       </c>
-      <c r="Y11" s="23">
+      <c r="Y11" s="13">
         <f t="shared" si="5"/>
         <v>3.6121204281670982E-2</v>
       </c>
-      <c r="Z11" s="23">
+      <c r="Z11" s="13">
         <f t="shared" si="6"/>
         <v>4.2943990136605797E-2</v>
       </c>
-      <c r="AB11" s="27">
+      <c r="AB11" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G8</f>
         <v>0</v>
       </c>
-      <c r="AC11" s="27">
+      <c r="AC11" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F8</f>
         <v>0</v>
       </c>
-      <c r="AD11" s="27">
+      <c r="AD11" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E8</f>
         <v>0</v>
       </c>
-      <c r="AE11" s="27">
+      <c r="AE11" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D8</f>
         <v>0</v>
       </c>
-      <c r="AF11" s="27">
+      <c r="AF11" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C8</f>
         <v>0</v>
       </c>
-      <c r="AG11" s="27">
+      <c r="AG11" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B8</f>
         <v>0</v>
       </c>
@@ -4209,51 +4232,51 @@
       <c r="T12" s="1">
         <v>-1.2999999999999999E-2</v>
       </c>
-      <c r="U12" s="23">
+      <c r="U12" s="13">
         <f t="shared" si="1"/>
         <v>6.4072061858232003E-4</v>
       </c>
-      <c r="V12" s="23">
+      <c r="V12" s="13">
         <f t="shared" si="2"/>
         <v>1.3623465740959901E-3</v>
       </c>
-      <c r="W12" s="23">
+      <c r="W12" s="13">
         <f t="shared" si="3"/>
         <v>9.8181705125270635E-4</v>
       </c>
-      <c r="X12" s="23">
+      <c r="X12" s="13">
         <f t="shared" si="4"/>
         <v>5.2246851225590252E-3</v>
       </c>
-      <c r="Y12" s="23">
+      <c r="Y12" s="13">
         <f t="shared" si="5"/>
         <v>4.3102192240533022E-2</v>
       </c>
-      <c r="Z12" s="23">
+      <c r="Z12" s="13">
         <f t="shared" si="6"/>
         <v>1.52450897933533E-2</v>
       </c>
-      <c r="AB12" s="27">
+      <c r="AB12" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G9</f>
         <v>0</v>
       </c>
-      <c r="AC12" s="27">
+      <c r="AC12" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F9</f>
         <v>0</v>
       </c>
-      <c r="AD12" s="27">
+      <c r="AD12" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E9</f>
         <v>0</v>
       </c>
-      <c r="AE12" s="27">
+      <c r="AE12" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D9</f>
         <v>0</v>
       </c>
-      <c r="AF12" s="27">
+      <c r="AF12" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C9</f>
         <v>0</v>
       </c>
-      <c r="AG12" s="27">
+      <c r="AG12" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B9</f>
         <v>0</v>
       </c>
@@ -4319,51 +4342,51 @@
       <c r="T13" s="1">
         <v>0</v>
       </c>
-      <c r="U13" s="23">
+      <c r="U13" s="13">
         <f t="shared" si="1"/>
         <v>2.1531186066567902E-3</v>
       </c>
-      <c r="V13" s="23">
+      <c r="V13" s="13">
         <f t="shared" si="2"/>
         <v>1.85897364281118E-3</v>
       </c>
-      <c r="W13" s="23">
+      <c r="W13" s="13">
         <f t="shared" si="3"/>
         <v>1.8817800445175004E-3</v>
       </c>
-      <c r="X13" s="23">
+      <c r="X13" s="13">
         <f t="shared" si="4"/>
         <v>5.8595346301180129E-3</v>
       </c>
-      <c r="Y13" s="23">
+      <c r="Y13" s="13">
         <f t="shared" si="5"/>
         <v>5.405756419502003E-2</v>
       </c>
-      <c r="Z13" s="23">
+      <c r="Z13" s="13">
         <f t="shared" si="6"/>
         <v>3.35876196622849E-2</v>
       </c>
-      <c r="AB13" s="27">
+      <c r="AB13" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G10</f>
         <v>0</v>
       </c>
-      <c r="AC13" s="27">
+      <c r="AC13" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F10</f>
         <v>0</v>
       </c>
-      <c r="AD13" s="27">
+      <c r="AD13" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E10</f>
         <v>0</v>
       </c>
-      <c r="AE13" s="27">
+      <c r="AE13" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D10</f>
         <v>0</v>
       </c>
-      <c r="AF13" s="27">
+      <c r="AF13" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C10</f>
         <v>0</v>
       </c>
-      <c r="AG13" s="27">
+      <c r="AG13" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B10</f>
         <v>0</v>
       </c>
@@ -4429,51 +4452,51 @@
       <c r="T14" s="1">
         <v>-0.76800000000000002</v>
       </c>
-      <c r="U14" s="23">
+      <c r="U14" s="13">
         <f t="shared" si="1"/>
         <v>7.7863028049029006E-4</v>
       </c>
-      <c r="V14" s="23">
+      <c r="V14" s="13">
         <f t="shared" si="2"/>
         <v>2.44569318598692E-3</v>
       </c>
-      <c r="W14" s="23">
+      <c r="W14" s="13">
         <f t="shared" si="3"/>
         <v>5.5269742361106766E-5</v>
       </c>
-      <c r="X14" s="23">
+      <c r="X14" s="13">
         <f t="shared" si="4"/>
         <v>3.694402702894295E-2</v>
       </c>
-      <c r="Y14" s="23">
+      <c r="Y14" s="13">
         <f t="shared" si="5"/>
         <v>6.674353092798202E-2</v>
       </c>
-      <c r="Z14" s="23">
+      <c r="Z14" s="13">
         <f t="shared" si="6"/>
         <v>2.128131026259E-2</v>
       </c>
-      <c r="AB14" s="27">
+      <c r="AB14" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G11</f>
         <v>0</v>
       </c>
-      <c r="AC14" s="27">
+      <c r="AC14" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F11</f>
         <v>0</v>
       </c>
-      <c r="AD14" s="27">
+      <c r="AD14" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E11</f>
         <v>0</v>
       </c>
-      <c r="AE14" s="27">
+      <c r="AE14" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D11</f>
         <v>0</v>
       </c>
-      <c r="AF14" s="27">
+      <c r="AF14" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C11</f>
         <v>0</v>
       </c>
-      <c r="AG14" s="27">
+      <c r="AG14" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B11</f>
         <v>0</v>
       </c>
@@ -4539,51 +4562,51 @@
       <c r="T15" s="1">
         <v>-0.1</v>
       </c>
-      <c r="U15" s="23">
+      <c r="U15" s="13">
         <f t="shared" si="1"/>
         <v>2.2744497053297803E-4</v>
       </c>
-      <c r="V15" s="23">
+      <c r="V15" s="13">
         <f t="shared" si="2"/>
         <v>1.3514636023268699E-4</v>
       </c>
-      <c r="W15" s="23">
+      <c r="W15" s="13">
         <f t="shared" si="3"/>
         <v>4.7966392857000384E-5</v>
       </c>
-      <c r="X15" s="23">
+      <c r="X15" s="13">
         <f t="shared" si="4"/>
         <v>5.2911493883239791E-3</v>
       </c>
-      <c r="Y15" s="23">
+      <c r="Y15" s="13">
         <f t="shared" si="5"/>
         <v>1.3738291089249982E-2</v>
       </c>
-      <c r="Z15" s="23">
+      <c r="Z15" s="13">
         <f t="shared" si="6"/>
         <v>4.7126291233810401E-3</v>
       </c>
-      <c r="AB15" s="27">
+      <c r="AB15" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G12</f>
         <v>0</v>
       </c>
-      <c r="AC15" s="27">
+      <c r="AC15" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F12</f>
         <v>0</v>
       </c>
-      <c r="AD15" s="27">
+      <c r="AD15" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E12</f>
         <v>0</v>
       </c>
-      <c r="AE15" s="27">
+      <c r="AE15" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D12</f>
         <v>0</v>
       </c>
-      <c r="AF15" s="27">
+      <c r="AF15" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C12</f>
         <v>0</v>
       </c>
-      <c r="AG15" s="27">
+      <c r="AG15" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B12</f>
         <v>0</v>
       </c>
@@ -4649,51 +4672,51 @@
       <c r="T16" s="1">
         <v>0</v>
       </c>
-      <c r="U16" s="23">
+      <c r="U16" s="13">
         <f t="shared" si="1"/>
         <v>1.05677347164601E-3</v>
       </c>
-      <c r="V16" s="23">
+      <c r="V16" s="13">
         <f t="shared" si="2"/>
         <v>1.7957310192287001E-3</v>
       </c>
-      <c r="W16" s="23">
+      <c r="W16" s="13">
         <f t="shared" si="3"/>
         <v>2.7426114366470022E-3</v>
       </c>
-      <c r="X16" s="23">
+      <c r="X16" s="13">
         <f t="shared" si="4"/>
         <v>4.2119719457204968E-2</v>
       </c>
-      <c r="Y16" s="23">
+      <c r="Y16" s="13">
         <f t="shared" si="5"/>
         <v>6.2059856742745972E-2</v>
       </c>
-      <c r="Z16" s="23">
+      <c r="Z16" s="13">
         <f t="shared" si="6"/>
         <v>1.8380418419838E-2</v>
       </c>
-      <c r="AB16" s="27">
+      <c r="AB16" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G13</f>
         <v>0</v>
       </c>
-      <c r="AC16" s="27">
+      <c r="AC16" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F13</f>
         <v>0</v>
       </c>
-      <c r="AD16" s="27">
+      <c r="AD16" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E13</f>
         <v>0</v>
       </c>
-      <c r="AE16" s="27">
+      <c r="AE16" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D13</f>
         <v>0</v>
       </c>
-      <c r="AF16" s="27">
+      <c r="AF16" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C13</f>
         <v>0</v>
       </c>
-      <c r="AG16" s="27">
+      <c r="AG16" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B13</f>
         <v>0</v>
       </c>
@@ -4759,51 +4782,51 @@
       <c r="T17" s="1">
         <v>0</v>
       </c>
-      <c r="U17" s="23">
+      <c r="U17" s="13">
         <f t="shared" si="1"/>
         <v>3.5343742929399001E-3</v>
       </c>
-      <c r="V17" s="23">
+      <c r="V17" s="13">
         <f t="shared" si="2"/>
         <v>3.7954235449433301E-3</v>
       </c>
-      <c r="W17" s="23">
+      <c r="W17" s="13">
         <f t="shared" si="3"/>
         <v>2.1551436498259968E-3</v>
       </c>
-      <c r="X17" s="23">
+      <c r="X17" s="13">
         <f t="shared" si="4"/>
         <v>2.0978067187708033E-2</v>
       </c>
-      <c r="Y17" s="23">
+      <c r="Y17" s="13">
         <f t="shared" si="5"/>
         <v>3.8367739546490032E-2</v>
       </c>
-      <c r="Z17" s="23">
+      <c r="Z17" s="13">
         <f t="shared" si="6"/>
         <v>2.4793863296508799E-2</v>
       </c>
-      <c r="AB17" s="27">
+      <c r="AB17" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G14</f>
         <v>0</v>
       </c>
-      <c r="AC17" s="27">
+      <c r="AC17" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F14</f>
         <v>0</v>
       </c>
-      <c r="AD17" s="27">
+      <c r="AD17" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E14</f>
         <v>0</v>
       </c>
-      <c r="AE17" s="27">
+      <c r="AE17" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D14</f>
         <v>0</v>
       </c>
-      <c r="AF17" s="27">
+      <c r="AF17" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C14</f>
         <v>0</v>
       </c>
-      <c r="AG17" s="27">
+      <c r="AG17" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B14</f>
         <v>0</v>
       </c>
@@ -4869,51 +4892,51 @@
       <c r="T18" s="1">
         <v>-1.028</v>
       </c>
-      <c r="U18" s="23">
+      <c r="U18" s="13">
         <f t="shared" si="1"/>
         <v>2.07396097829819E-3</v>
       </c>
-      <c r="V18" s="23">
+      <c r="V18" s="13">
         <f t="shared" si="2"/>
         <v>4.1180973667579897E-3</v>
       </c>
-      <c r="W18" s="23">
+      <c r="W18" s="13">
         <f t="shared" si="3"/>
         <v>8.0948865436508005E-3</v>
       </c>
-      <c r="X18" s="23">
+      <c r="X18" s="13">
         <f t="shared" si="4"/>
         <v>0.16524015895468802</v>
       </c>
-      <c r="Y18" s="23">
+      <c r="Y18" s="13">
         <f t="shared" si="5"/>
         <v>6.7497218058739983E-2</v>
       </c>
-      <c r="Z18" s="23">
+      <c r="Z18" s="13">
         <f t="shared" si="6"/>
         <v>2.9061765461044296E-2</v>
       </c>
-      <c r="AB18" s="27">
+      <c r="AB18" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G15</f>
         <v>0</v>
       </c>
-      <c r="AC18" s="27">
+      <c r="AC18" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F15</f>
         <v>0</v>
       </c>
-      <c r="AD18" s="27">
+      <c r="AD18" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E15</f>
         <v>0</v>
       </c>
-      <c r="AE18" s="27">
+      <c r="AE18" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D15</f>
         <v>0</v>
       </c>
-      <c r="AF18" s="27">
+      <c r="AF18" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C15</f>
         <v>0</v>
       </c>
-      <c r="AG18" s="27">
+      <c r="AG18" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B15</f>
         <v>0</v>
       </c>
@@ -4979,55 +5002,55 @@
       <c r="T19" s="1">
         <v>-0.41199999999999998</v>
       </c>
-      <c r="U19" s="23">
+      <c r="U19" s="13">
         <f t="shared" si="1"/>
         <v>2.3456981168881699E-3</v>
       </c>
-      <c r="V19" s="23">
+      <c r="V19" s="13">
         <f t="shared" si="2"/>
         <v>4.0980054929747598E-4</v>
       </c>
-      <c r="W19" s="23">
+      <c r="W19" s="13">
         <f t="shared" si="3"/>
         <v>2.9979691053435981E-3</v>
       </c>
-      <c r="X19" s="23">
+      <c r="X19" s="13">
         <f t="shared" si="4"/>
         <v>2.0339334908391904E-2</v>
       </c>
-      <c r="Y19" s="23">
+      <c r="Y19" s="13">
         <f t="shared" si="5"/>
         <v>6.2761498856319653E-3</v>
       </c>
-      <c r="Z19" s="23">
+      <c r="Z19" s="13">
         <f t="shared" si="6"/>
         <v>1.286653510315857E-2</v>
       </c>
-      <c r="AB19" s="27">
+      <c r="AB19" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G16</f>
         <v>0</v>
       </c>
-      <c r="AC19" s="27">
+      <c r="AC19" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F16</f>
         <v>0</v>
       </c>
-      <c r="AD19" s="27">
+      <c r="AD19" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E16</f>
         <v>0</v>
       </c>
-      <c r="AE19" s="27">
+      <c r="AE19" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D16</f>
         <v>0</v>
       </c>
-      <c r="AF19" s="27">
+      <c r="AF19" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C16</f>
         <v>0</v>
       </c>
-      <c r="AG19" s="27">
+      <c r="AG19" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B16</f>
         <v>0</v>
       </c>
-      <c r="AI19" s="4" t="s">
+      <c r="AI19" s="3" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5092,51 +5115,51 @@
       <c r="T20" s="1">
         <v>-1.222</v>
       </c>
-      <c r="U20" s="23">
+      <c r="U20" s="13">
         <f t="shared" si="1"/>
         <v>1.68689796118319E-3</v>
       </c>
-      <c r="V20" s="23">
+      <c r="V20" s="13">
         <f t="shared" si="2"/>
         <v>4.1812268346476597E-3</v>
       </c>
-      <c r="W20" s="23">
+      <c r="W20" s="13">
         <f t="shared" si="3"/>
         <v>9.1381179317123057E-3</v>
       </c>
-      <c r="X20" s="23">
+      <c r="X20" s="13">
         <f t="shared" si="4"/>
         <v>0.45588083110736999</v>
       </c>
-      <c r="Y20" s="23">
+      <c r="Y20" s="13">
         <f t="shared" si="5"/>
         <v>5.7684503347076033E-2</v>
       </c>
-      <c r="Z20" s="23">
+      <c r="Z20" s="13">
         <f t="shared" si="6"/>
         <v>2.4679125337677001E-2</v>
       </c>
-      <c r="AB20" s="27">
+      <c r="AB20" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G17</f>
         <v>0</v>
       </c>
-      <c r="AC20" s="27">
+      <c r="AC20" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F17</f>
         <v>0</v>
       </c>
-      <c r="AD20" s="27">
+      <c r="AD20" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E17</f>
         <v>0</v>
       </c>
-      <c r="AE20" s="27">
+      <c r="AE20" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D17</f>
         <v>0</v>
       </c>
-      <c r="AF20" s="27">
+      <c r="AF20" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C17</f>
         <v>0</v>
       </c>
-      <c r="AG20" s="27">
+      <c r="AG20" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B17</f>
         <v>0</v>
       </c>
@@ -5202,51 +5225,51 @@
       <c r="T21" s="1">
         <v>-0.29599999999999999</v>
       </c>
-      <c r="U21" s="23">
+      <c r="U21" s="13">
         <f t="shared" si="1"/>
         <v>1.9370874845967999E-3</v>
       </c>
-      <c r="V21" s="23">
+      <c r="V21" s="13">
         <f t="shared" si="2"/>
         <v>1.4901723410939501E-3</v>
       </c>
-      <c r="W21" s="23">
+      <c r="W21" s="13">
         <f t="shared" si="3"/>
         <v>2.2562255286490973E-3</v>
       </c>
-      <c r="X21" s="23">
+      <c r="X21" s="13">
         <f t="shared" si="4"/>
         <v>2.9524263471996992E-2</v>
       </c>
-      <c r="Y21" s="23">
+      <c r="Y21" s="13">
         <f t="shared" si="5"/>
         <v>5.9068764662109086E-2</v>
       </c>
-      <c r="Z21" s="23">
+      <c r="Z21" s="13">
         <f t="shared" si="6"/>
         <v>3.7120485021530203E-2</v>
       </c>
-      <c r="AB21" s="27">
+      <c r="AB21" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G18</f>
         <v>0</v>
       </c>
-      <c r="AC21" s="27">
+      <c r="AC21" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F18</f>
         <v>0</v>
       </c>
-      <c r="AD21" s="27">
+      <c r="AD21" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E18</f>
         <v>0</v>
       </c>
-      <c r="AE21" s="27">
+      <c r="AE21" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D18</f>
         <v>0</v>
       </c>
-      <c r="AF21" s="27">
+      <c r="AF21" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C18</f>
         <v>0</v>
       </c>
-      <c r="AG21" s="27">
+      <c r="AG21" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B18</f>
         <v>0</v>
       </c>
@@ -5312,51 +5335,51 @@
       <c r="T22" s="1">
         <v>-0.125</v>
       </c>
-      <c r="U22" s="23">
+      <c r="U22" s="13">
         <f t="shared" si="1"/>
         <v>4.2762093939942693E-4</v>
       </c>
-      <c r="V22" s="23">
+      <c r="V22" s="13">
         <f t="shared" si="2"/>
         <v>7.2619960149201198E-4</v>
       </c>
-      <c r="W22" s="23">
+      <c r="W22" s="13">
         <f t="shared" si="3"/>
         <v>1.723210445001221E-3</v>
       </c>
-      <c r="X22" s="23">
+      <c r="X22" s="13">
         <f t="shared" si="4"/>
         <v>7.960889352020023E-3</v>
       </c>
-      <c r="Y22" s="23">
+      <c r="Y22" s="13">
         <f t="shared" si="5"/>
         <v>5.2839390156592947E-3</v>
       </c>
-      <c r="Z22" s="23">
+      <c r="Z22" s="13">
         <f t="shared" si="6"/>
         <v>1.4320642188307999E-2</v>
       </c>
-      <c r="AB22" s="27">
+      <c r="AB22" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G19</f>
         <v>0</v>
       </c>
-      <c r="AC22" s="27">
+      <c r="AC22" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F19</f>
         <v>0</v>
       </c>
-      <c r="AD22" s="27">
+      <c r="AD22" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E19</f>
         <v>0</v>
       </c>
-      <c r="AE22" s="27">
+      <c r="AE22" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D19</f>
         <v>0</v>
       </c>
-      <c r="AF22" s="27">
+      <c r="AF22" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C19</f>
         <v>0</v>
       </c>
-      <c r="AG22" s="27">
+      <c r="AG22" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B19</f>
         <v>0</v>
       </c>
@@ -5422,51 +5445,51 @@
       <c r="T23" s="1">
         <v>-0.53900000000000003</v>
       </c>
-      <c r="U23" s="23">
+      <c r="U23" s="13">
         <f t="shared" si="1"/>
         <v>7.1233522392327004E-4</v>
       </c>
-      <c r="V23" s="23">
+      <c r="V23" s="13">
         <f t="shared" si="2"/>
         <v>1.8782845663913399E-3</v>
       </c>
-      <c r="W23" s="23">
+      <c r="W23" s="13">
         <f t="shared" si="3"/>
         <v>3.6965311917569812E-4</v>
       </c>
-      <c r="X23" s="23">
+      <c r="X23" s="13">
         <f t="shared" si="4"/>
         <v>6.7251414031679335E-3</v>
       </c>
-      <c r="Y23" s="23">
+      <c r="Y23" s="13">
         <f t="shared" si="5"/>
         <v>2.1228399006401E-2</v>
       </c>
-      <c r="Z23" s="23">
+      <c r="Z23" s="13">
         <f t="shared" si="6"/>
         <v>1.35616384801613E-2</v>
       </c>
-      <c r="AB23" s="27">
+      <c r="AB23" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G20</f>
         <v>0</v>
       </c>
-      <c r="AC23" s="27">
+      <c r="AC23" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F20</f>
         <v>0</v>
       </c>
-      <c r="AD23" s="27">
+      <c r="AD23" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E20</f>
         <v>0</v>
       </c>
-      <c r="AE23" s="27">
+      <c r="AE23" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D20</f>
         <v>0</v>
       </c>
-      <c r="AF23" s="27">
+      <c r="AF23" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C20</f>
         <v>0</v>
       </c>
-      <c r="AG23" s="27">
+      <c r="AG23" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B20</f>
         <v>0</v>
       </c>
@@ -5502,33 +5525,33 @@
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
-      <c r="U24" s="23"/>
-      <c r="V24" s="23"/>
-      <c r="W24" s="23"/>
-      <c r="X24" s="23"/>
-      <c r="Y24" s="23"/>
-      <c r="Z24" s="23"/>
-      <c r="AB24" s="27">
+      <c r="U24" s="13"/>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="13"/>
+      <c r="Y24" s="13"/>
+      <c r="Z24" s="13"/>
+      <c r="AB24" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G21</f>
         <v>0</v>
       </c>
-      <c r="AC24" s="27">
+      <c r="AC24" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F21</f>
         <v>0</v>
       </c>
-      <c r="AD24" s="27">
+      <c r="AD24" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E21</f>
         <v>0</v>
       </c>
-      <c r="AE24" s="27">
+      <c r="AE24" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D21</f>
         <v>0</v>
       </c>
-      <c r="AF24" s="27">
+      <c r="AF24" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C21</f>
         <v>0</v>
       </c>
-      <c r="AG24" s="27">
+      <c r="AG24" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B21</f>
         <v>0</v>
       </c>
@@ -5564,33 +5587,33 @@
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
-      <c r="U25" s="23"/>
-      <c r="V25" s="23"/>
-      <c r="W25" s="23"/>
-      <c r="X25" s="23"/>
-      <c r="Y25" s="23"/>
-      <c r="Z25" s="23"/>
-      <c r="AB25" s="27">
+      <c r="U25" s="13"/>
+      <c r="V25" s="13"/>
+      <c r="W25" s="13"/>
+      <c r="X25" s="13"/>
+      <c r="Y25" s="13"/>
+      <c r="Z25" s="13"/>
+      <c r="AB25" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G22</f>
         <v>0</v>
       </c>
-      <c r="AC25" s="27">
+      <c r="AC25" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F22</f>
         <v>0</v>
       </c>
-      <c r="AD25" s="27">
+      <c r="AD25" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E22</f>
         <v>0</v>
       </c>
-      <c r="AE25" s="27">
+      <c r="AE25" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D22</f>
         <v>0</v>
       </c>
-      <c r="AF25" s="27">
+      <c r="AF25" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C22</f>
         <v>0</v>
       </c>
-      <c r="AG25" s="27">
+      <c r="AG25" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B22</f>
         <v>0</v>
       </c>
@@ -5626,33 +5649,33 @@
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
-      <c r="U26" s="23"/>
-      <c r="V26" s="23"/>
-      <c r="W26" s="23"/>
-      <c r="X26" s="23"/>
-      <c r="Y26" s="23"/>
-      <c r="Z26" s="23"/>
-      <c r="AB26" s="27">
+      <c r="U26" s="13"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="13"/>
+      <c r="X26" s="13"/>
+      <c r="Y26" s="13"/>
+      <c r="Z26" s="13"/>
+      <c r="AB26" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G23</f>
         <v>0</v>
       </c>
-      <c r="AC26" s="27">
+      <c r="AC26" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F23</f>
         <v>0</v>
       </c>
-      <c r="AD26" s="27">
+      <c r="AD26" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E23</f>
         <v>0</v>
       </c>
-      <c r="AE26" s="27">
+      <c r="AE26" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D23</f>
         <v>0</v>
       </c>
-      <c r="AF26" s="27">
+      <c r="AF26" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C23</f>
         <v>0</v>
       </c>
-      <c r="AG26" s="27">
+      <c r="AG26" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B23</f>
         <v>0</v>
       </c>
@@ -5688,33 +5711,33 @@
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
-      <c r="U27" s="23"/>
-      <c r="V27" s="23"/>
-      <c r="W27" s="23"/>
-      <c r="X27" s="23"/>
-      <c r="Y27" s="23"/>
-      <c r="Z27" s="23"/>
-      <c r="AB27" s="27">
+      <c r="U27" s="13"/>
+      <c r="V27" s="13"/>
+      <c r="W27" s="13"/>
+      <c r="X27" s="13"/>
+      <c r="Y27" s="13"/>
+      <c r="Z27" s="13"/>
+      <c r="AB27" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G24</f>
         <v>0</v>
       </c>
-      <c r="AC27" s="27">
+      <c r="AC27" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F24</f>
         <v>0</v>
       </c>
-      <c r="AD27" s="27">
+      <c r="AD27" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E24</f>
         <v>0</v>
       </c>
-      <c r="AE27" s="27">
+      <c r="AE27" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D24</f>
         <v>0</v>
       </c>
-      <c r="AF27" s="27">
+      <c r="AF27" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C24</f>
         <v>0</v>
       </c>
-      <c r="AG27" s="27">
+      <c r="AG27" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B24</f>
         <v>0</v>
       </c>
@@ -5750,33 +5773,33 @@
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
-      <c r="U28" s="23"/>
-      <c r="V28" s="23"/>
-      <c r="W28" s="23"/>
-      <c r="X28" s="23"/>
-      <c r="Y28" s="23"/>
-      <c r="Z28" s="23"/>
-      <c r="AB28" s="27">
+      <c r="U28" s="13"/>
+      <c r="V28" s="13"/>
+      <c r="W28" s="13"/>
+      <c r="X28" s="13"/>
+      <c r="Y28" s="13"/>
+      <c r="Z28" s="13"/>
+      <c r="AB28" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G25</f>
         <v>0</v>
       </c>
-      <c r="AC28" s="27">
+      <c r="AC28" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F25</f>
         <v>0</v>
       </c>
-      <c r="AD28" s="27">
+      <c r="AD28" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E25</f>
         <v>0</v>
       </c>
-      <c r="AE28" s="27">
+      <c r="AE28" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D25</f>
         <v>0</v>
       </c>
-      <c r="AF28" s="27">
+      <c r="AF28" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C25</f>
         <v>0</v>
       </c>
-      <c r="AG28" s="27">
+      <c r="AG28" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B25</f>
         <v>0</v>
       </c>
@@ -5812,33 +5835,33 @@
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
-      <c r="U29" s="23"/>
-      <c r="V29" s="23"/>
-      <c r="W29" s="23"/>
-      <c r="X29" s="23"/>
-      <c r="Y29" s="23"/>
-      <c r="Z29" s="23"/>
-      <c r="AB29" s="27">
+      <c r="U29" s="13"/>
+      <c r="V29" s="13"/>
+      <c r="W29" s="13"/>
+      <c r="X29" s="13"/>
+      <c r="Y29" s="13"/>
+      <c r="Z29" s="13"/>
+      <c r="AB29" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G26</f>
         <v>0</v>
       </c>
-      <c r="AC29" s="27">
+      <c r="AC29" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F26</f>
         <v>0</v>
       </c>
-      <c r="AD29" s="27">
+      <c r="AD29" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E26</f>
         <v>0</v>
       </c>
-      <c r="AE29" s="27">
+      <c r="AE29" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D26</f>
         <v>0</v>
       </c>
-      <c r="AF29" s="27">
+      <c r="AF29" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C26</f>
         <v>0</v>
       </c>
-      <c r="AG29" s="27">
+      <c r="AG29" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B26</f>
         <v>0</v>
       </c>
@@ -5874,33 +5897,33 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
-      <c r="U30" s="23"/>
-      <c r="V30" s="23"/>
-      <c r="W30" s="23"/>
-      <c r="X30" s="23"/>
-      <c r="Y30" s="23"/>
-      <c r="Z30" s="23"/>
-      <c r="AB30" s="27">
+      <c r="U30" s="13"/>
+      <c r="V30" s="13"/>
+      <c r="W30" s="13"/>
+      <c r="X30" s="13"/>
+      <c r="Y30" s="13"/>
+      <c r="Z30" s="13"/>
+      <c r="AB30" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G27</f>
         <v>0</v>
       </c>
-      <c r="AC30" s="27">
+      <c r="AC30" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F27</f>
         <v>0</v>
       </c>
-      <c r="AD30" s="27">
+      <c r="AD30" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E27</f>
         <v>0</v>
       </c>
-      <c r="AE30" s="27">
+      <c r="AE30" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D27</f>
         <v>0</v>
       </c>
-      <c r="AF30" s="27">
+      <c r="AF30" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C27</f>
         <v>0</v>
       </c>
-      <c r="AG30" s="27">
+      <c r="AG30" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B27</f>
         <v>0</v>
       </c>
@@ -5936,33 +5959,33 @@
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
-      <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
-      <c r="W31" s="23"/>
-      <c r="X31" s="23"/>
-      <c r="Y31" s="23"/>
-      <c r="Z31" s="23"/>
-      <c r="AB31" s="27">
+      <c r="U31" s="13"/>
+      <c r="V31" s="13"/>
+      <c r="W31" s="13"/>
+      <c r="X31" s="13"/>
+      <c r="Y31" s="13"/>
+      <c r="Z31" s="13"/>
+      <c r="AB31" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G28</f>
         <v>0</v>
       </c>
-      <c r="AC31" s="27">
+      <c r="AC31" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F28</f>
         <v>0</v>
       </c>
-      <c r="AD31" s="27">
+      <c r="AD31" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E28</f>
         <v>0</v>
       </c>
-      <c r="AE31" s="27">
+      <c r="AE31" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D28</f>
         <v>0</v>
       </c>
-      <c r="AF31" s="27">
+      <c r="AF31" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C28</f>
         <v>0</v>
       </c>
-      <c r="AG31" s="27">
+      <c r="AG31" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B28</f>
         <v>0</v>
       </c>
@@ -5998,33 +6021,33 @@
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
-      <c r="U32" s="23"/>
-      <c r="V32" s="23"/>
-      <c r="W32" s="23"/>
-      <c r="X32" s="23"/>
-      <c r="Y32" s="23"/>
-      <c r="Z32" s="23"/>
-      <c r="AB32" s="27">
+      <c r="U32" s="13"/>
+      <c r="V32" s="13"/>
+      <c r="W32" s="13"/>
+      <c r="X32" s="13"/>
+      <c r="Y32" s="13"/>
+      <c r="Z32" s="13"/>
+      <c r="AB32" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G29</f>
         <v>0</v>
       </c>
-      <c r="AC32" s="27">
+      <c r="AC32" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F29</f>
         <v>0</v>
       </c>
-      <c r="AD32" s="27">
+      <c r="AD32" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E29</f>
         <v>0</v>
       </c>
-      <c r="AE32" s="27">
+      <c r="AE32" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D29</f>
         <v>0</v>
       </c>
-      <c r="AF32" s="27">
+      <c r="AF32" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C29</f>
         <v>0</v>
       </c>
-      <c r="AG32" s="27">
+      <c r="AG32" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B29</f>
         <v>0</v>
       </c>
@@ -6060,1021 +6083,949 @@
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
-      <c r="U33" s="23"/>
-      <c r="V33" s="23"/>
-      <c r="W33" s="23"/>
-      <c r="X33" s="23"/>
-      <c r="Y33" s="23"/>
-      <c r="Z33" s="23"/>
-      <c r="AB33" s="27">
+      <c r="U33" s="13"/>
+      <c r="V33" s="13"/>
+      <c r="W33" s="13"/>
+      <c r="X33" s="13"/>
+      <c r="Y33" s="13"/>
+      <c r="Z33" s="13"/>
+      <c r="AB33" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G30</f>
         <v>0</v>
       </c>
-      <c r="AC33" s="27">
+      <c r="AC33" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F30</f>
         <v>0</v>
       </c>
-      <c r="AD33" s="27">
+      <c r="AD33" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E30</f>
         <v>0</v>
       </c>
-      <c r="AE33" s="27">
+      <c r="AE33" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D30</f>
         <v>0</v>
       </c>
-      <c r="AF33" s="27">
+      <c r="AF33" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C30</f>
         <v>0</v>
       </c>
-      <c r="AG33" s="27">
+      <c r="AG33" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B30</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A34" s="28"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="28"/>
-      <c r="N34" s="28"/>
-      <c r="O34" s="28"/>
-      <c r="P34" s="28"/>
-      <c r="Q34" s="28"/>
-      <c r="R34" s="28"/>
-      <c r="S34" s="28"/>
-      <c r="T34" s="28"/>
-      <c r="U34" s="23"/>
-      <c r="V34" s="23"/>
-      <c r="W34" s="23"/>
-      <c r="X34" s="23"/>
-      <c r="Y34" s="23"/>
-      <c r="Z34" s="23"/>
-      <c r="AB34" s="27">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="18"/>
+      <c r="Q34" s="18"/>
+      <c r="R34" s="18"/>
+      <c r="S34" s="18"/>
+      <c r="T34" s="18"/>
+      <c r="U34" s="13"/>
+      <c r="V34" s="13"/>
+      <c r="W34" s="13"/>
+      <c r="X34" s="13"/>
+      <c r="Y34" s="13"/>
+      <c r="Z34" s="13"/>
+      <c r="AB34" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G31</f>
         <v>0</v>
       </c>
-      <c r="AC34" s="27">
+      <c r="AC34" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F31</f>
         <v>0</v>
       </c>
-      <c r="AD34" s="27">
+      <c r="AD34" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E31</f>
         <v>0</v>
       </c>
-      <c r="AE34" s="27">
+      <c r="AE34" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D31</f>
         <v>0</v>
       </c>
-      <c r="AF34" s="27">
+      <c r="AF34" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C31</f>
         <v>0</v>
       </c>
-      <c r="AG34" s="27">
+      <c r="AG34" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B31</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A35" s="28"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28"/>
-      <c r="N35" s="28"/>
-      <c r="O35" s="28"/>
-      <c r="P35" s="28"/>
-      <c r="Q35" s="28"/>
-      <c r="R35" s="28"/>
-      <c r="S35" s="28"/>
-      <c r="T35" s="28"/>
-      <c r="U35" s="23"/>
-      <c r="V35" s="23"/>
-      <c r="W35" s="23"/>
-      <c r="X35" s="23"/>
-      <c r="Y35" s="23"/>
-      <c r="Z35" s="23"/>
-      <c r="AB35" s="27">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="18"/>
+      <c r="R35" s="18"/>
+      <c r="S35" s="18"/>
+      <c r="T35" s="18"/>
+      <c r="U35" s="13"/>
+      <c r="V35" s="13"/>
+      <c r="W35" s="13"/>
+      <c r="X35" s="13"/>
+      <c r="Y35" s="13"/>
+      <c r="Z35" s="13"/>
+      <c r="AB35" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G32</f>
         <v>0</v>
       </c>
-      <c r="AC35" s="27">
+      <c r="AC35" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F32</f>
         <v>0</v>
       </c>
-      <c r="AD35" s="27">
+      <c r="AD35" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E32</f>
         <v>0</v>
       </c>
-      <c r="AE35" s="27">
+      <c r="AE35" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D32</f>
         <v>0</v>
       </c>
-      <c r="AF35" s="27">
+      <c r="AF35" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C32</f>
         <v>0</v>
       </c>
-      <c r="AG35" s="27">
+      <c r="AG35" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B32</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A36" s="28"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="28"/>
-      <c r="N36" s="28"/>
-      <c r="O36" s="28"/>
-      <c r="P36" s="28"/>
-      <c r="Q36" s="28"/>
-      <c r="R36" s="28"/>
-      <c r="S36" s="28"/>
-      <c r="T36" s="28"/>
-      <c r="U36" s="23"/>
-      <c r="V36" s="23"/>
-      <c r="W36" s="23"/>
-      <c r="X36" s="23"/>
-      <c r="Y36" s="23"/>
-      <c r="Z36" s="23"/>
-      <c r="AB36" s="27">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="18"/>
+      <c r="Q36" s="18"/>
+      <c r="R36" s="18"/>
+      <c r="S36" s="18"/>
+      <c r="T36" s="18"/>
+      <c r="U36" s="13"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+      <c r="X36" s="13"/>
+      <c r="Y36" s="13"/>
+      <c r="Z36" s="13"/>
+      <c r="AB36" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G33</f>
         <v>0</v>
       </c>
-      <c r="AC36" s="27">
+      <c r="AC36" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F33</f>
         <v>0</v>
       </c>
-      <c r="AD36" s="27">
+      <c r="AD36" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E33</f>
         <v>0</v>
       </c>
-      <c r="AE36" s="27">
+      <c r="AE36" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D33</f>
         <v>0</v>
       </c>
-      <c r="AF36" s="27">
+      <c r="AF36" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C33</f>
         <v>0</v>
       </c>
-      <c r="AG36" s="27">
+      <c r="AG36" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B33</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A37" s="28"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
-      <c r="U37" s="23"/>
-      <c r="V37" s="23"/>
-      <c r="W37" s="23"/>
-      <c r="X37" s="23"/>
-      <c r="Y37" s="23"/>
-      <c r="Z37" s="23"/>
-      <c r="AB37" s="27">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="18"/>
+      <c r="R37" s="18"/>
+      <c r="S37" s="18"/>
+      <c r="T37" s="18"/>
+      <c r="U37" s="13"/>
+      <c r="V37" s="13"/>
+      <c r="W37" s="13"/>
+      <c r="X37" s="13"/>
+      <c r="Y37" s="13"/>
+      <c r="Z37" s="13"/>
+      <c r="AB37" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G34</f>
         <v>0</v>
       </c>
-      <c r="AC37" s="27">
+      <c r="AC37" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F34</f>
         <v>0</v>
       </c>
-      <c r="AD37" s="27">
+      <c r="AD37" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E34</f>
         <v>0</v>
       </c>
-      <c r="AE37" s="27">
+      <c r="AE37" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D34</f>
         <v>0</v>
       </c>
-      <c r="AF37" s="27">
+      <c r="AF37" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C34</f>
         <v>0</v>
       </c>
-      <c r="AG37" s="27">
+      <c r="AG37" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B34</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A38" s="28"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="28"/>
-      <c r="N38" s="28"/>
-      <c r="O38" s="28"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="28"/>
-      <c r="R38" s="28"/>
-      <c r="S38" s="28"/>
-      <c r="T38" s="28"/>
-      <c r="U38" s="23"/>
-      <c r="V38" s="23"/>
-      <c r="W38" s="23"/>
-      <c r="X38" s="23"/>
-      <c r="Y38" s="23"/>
-      <c r="Z38" s="23"/>
-      <c r="AB38" s="27">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="18"/>
+      <c r="S38" s="18"/>
+      <c r="T38" s="18"/>
+      <c r="U38" s="13"/>
+      <c r="V38" s="13"/>
+      <c r="W38" s="13"/>
+      <c r="X38" s="13"/>
+      <c r="Y38" s="13"/>
+      <c r="Z38" s="13"/>
+      <c r="AB38" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G35</f>
         <v>0</v>
       </c>
-      <c r="AC38" s="27">
+      <c r="AC38" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F35</f>
         <v>0</v>
       </c>
-      <c r="AD38" s="27">
+      <c r="AD38" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E35</f>
         <v>0</v>
       </c>
-      <c r="AE38" s="27">
+      <c r="AE38" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D35</f>
         <v>0</v>
       </c>
-      <c r="AF38" s="27">
+      <c r="AF38" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C35</f>
         <v>0</v>
       </c>
-      <c r="AG38" s="27">
+      <c r="AG38" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B35</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A39" s="28"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="28"/>
-      <c r="N39" s="28"/>
-      <c r="O39" s="28"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="28"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="28"/>
-      <c r="T39" s="28"/>
-      <c r="U39" s="23"/>
-      <c r="V39" s="23"/>
-      <c r="W39" s="23"/>
-      <c r="X39" s="23"/>
-      <c r="Y39" s="23"/>
-      <c r="Z39" s="23"/>
-      <c r="AB39" s="27">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="18"/>
+      <c r="Q39" s="18"/>
+      <c r="R39" s="18"/>
+      <c r="S39" s="18"/>
+      <c r="T39" s="18"/>
+      <c r="U39" s="13"/>
+      <c r="V39" s="13"/>
+      <c r="W39" s="13"/>
+      <c r="X39" s="13"/>
+      <c r="Y39" s="13"/>
+      <c r="Z39" s="13"/>
+      <c r="AB39" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G36</f>
         <v>0</v>
       </c>
-      <c r="AC39" s="27">
+      <c r="AC39" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F36</f>
         <v>0</v>
       </c>
-      <c r="AD39" s="27">
+      <c r="AD39" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E36</f>
         <v>0</v>
       </c>
-      <c r="AE39" s="27">
+      <c r="AE39" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D36</f>
         <v>0</v>
       </c>
-      <c r="AF39" s="27">
+      <c r="AF39" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C36</f>
         <v>0</v>
       </c>
-      <c r="AG39" s="27">
+      <c r="AG39" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B36</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A40" s="28"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28"/>
-      <c r="T40" s="28"/>
-      <c r="U40" s="23"/>
-      <c r="V40" s="23"/>
-      <c r="W40" s="23"/>
-      <c r="X40" s="23"/>
-      <c r="Y40" s="23"/>
-      <c r="Z40" s="23"/>
-      <c r="AB40" s="27">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="18"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="18"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="13"/>
+      <c r="V40" s="13"/>
+      <c r="W40" s="13"/>
+      <c r="X40" s="13"/>
+      <c r="Y40" s="13"/>
+      <c r="Z40" s="13"/>
+      <c r="AB40" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G37</f>
         <v>0</v>
       </c>
-      <c r="AC40" s="27">
+      <c r="AC40" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F37</f>
         <v>0</v>
       </c>
-      <c r="AD40" s="27">
+      <c r="AD40" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E37</f>
         <v>0</v>
       </c>
-      <c r="AE40" s="27">
+      <c r="AE40" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D37</f>
         <v>0</v>
       </c>
-      <c r="AF40" s="27">
+      <c r="AF40" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C37</f>
         <v>0</v>
       </c>
-      <c r="AG40" s="27">
+      <c r="AG40" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B37</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A41" s="29"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="29"/>
-      <c r="I41" s="29"/>
-      <c r="J41" s="29"/>
-      <c r="K41" s="29"/>
-      <c r="L41" s="29"/>
-      <c r="M41" s="29"/>
-      <c r="N41" s="29"/>
-      <c r="O41" s="29"/>
-      <c r="P41" s="29"/>
-      <c r="Q41" s="29"/>
-      <c r="R41" s="29"/>
-      <c r="S41" s="29"/>
-      <c r="T41" s="29"/>
-      <c r="U41" s="30"/>
-      <c r="V41" s="30"/>
-      <c r="W41" s="30"/>
-      <c r="X41" s="30"/>
-      <c r="Y41" s="30"/>
-      <c r="Z41" s="30"/>
-      <c r="AB41" s="27">
+      <c r="A41" s="19"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="19"/>
+      <c r="O41" s="19"/>
+      <c r="P41" s="19"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="19"/>
+      <c r="S41" s="19"/>
+      <c r="T41" s="19"/>
+      <c r="AB41" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G38</f>
         <v>-4.6970417315606002E-6</v>
       </c>
-      <c r="AC41" s="27">
+      <c r="AC41" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F38</f>
         <v>1.0438450772198799E-5</v>
       </c>
-      <c r="AD41" s="27">
+      <c r="AD41" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E38</f>
         <v>1.7066902273654701E-6</v>
       </c>
-      <c r="AE41" s="27">
+      <c r="AE41" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D38</f>
         <v>5.8085650380235199E-5</v>
       </c>
-      <c r="AF41" s="27">
+      <c r="AF41" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C38</f>
         <v>-7.8196363756433097E-4</v>
       </c>
-      <c r="AG41" s="27">
+      <c r="AG41" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B38</f>
         <v>1.2485386105254301E-4</v>
       </c>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A42" s="29"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="29"/>
-      <c r="J42" s="29"/>
-      <c r="K42" s="29"/>
-      <c r="L42" s="29"/>
-      <c r="M42" s="29"/>
-      <c r="N42" s="29"/>
-      <c r="O42" s="29"/>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="29"/>
-      <c r="R42" s="29"/>
-      <c r="S42" s="29"/>
-      <c r="T42" s="29"/>
-      <c r="U42" s="30"/>
-      <c r="V42" s="30"/>
-      <c r="W42" s="30"/>
-      <c r="X42" s="30"/>
-      <c r="Y42" s="30"/>
-      <c r="Z42" s="30"/>
-      <c r="AB42" s="27">
+      <c r="A42" s="19"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+      <c r="M42" s="19"/>
+      <c r="N42" s="19"/>
+      <c r="O42" s="19"/>
+      <c r="P42" s="19"/>
+      <c r="Q42" s="19"/>
+      <c r="R42" s="19"/>
+      <c r="S42" s="19"/>
+      <c r="T42" s="19"/>
+      <c r="AB42" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G39</f>
         <v>-9.1163394972681999E-4</v>
       </c>
-      <c r="AC42" s="27">
+      <c r="AC42" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F39</f>
         <v>-1.0851300321519401E-3</v>
       </c>
-      <c r="AD42" s="27">
+      <c r="AD42" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E39</f>
         <v>-2.5136896874755599E-3</v>
       </c>
-      <c r="AE42" s="27">
+      <c r="AE42" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D39</f>
         <v>-0.19703710079193101</v>
       </c>
-      <c r="AF42" s="27">
+      <c r="AF42" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C39</f>
         <v>-0.12924839556217199</v>
       </c>
-      <c r="AG42" s="27">
+      <c r="AG42" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B39</f>
         <v>8.4088072180748003E-3</v>
       </c>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A43" s="29"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="30"/>
-      <c r="V43" s="30"/>
-      <c r="W43" s="30"/>
-      <c r="X43" s="30"/>
-      <c r="Y43" s="30"/>
-      <c r="Z43" s="30"/>
-      <c r="AB43" s="27">
+      <c r="A43" s="19"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="19"/>
+      <c r="M43" s="19"/>
+      <c r="N43" s="19"/>
+      <c r="O43" s="19"/>
+      <c r="P43" s="19"/>
+      <c r="Q43" s="19"/>
+      <c r="R43" s="19"/>
+      <c r="S43" s="19"/>
+      <c r="T43" s="19"/>
+      <c r="AB43" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G40</f>
         <v>-2.39273207262158E-3</v>
       </c>
-      <c r="AC43" s="27">
+      <c r="AC43" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F40</f>
         <v>-3.4488118253648298E-3</v>
       </c>
-      <c r="AD43" s="27">
+      <c r="AD43" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E40</f>
         <v>-2.6666743680834801E-2</v>
       </c>
-      <c r="AE43" s="27">
+      <c r="AE43" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D40</f>
         <v>-2.8852019459009198E-2</v>
       </c>
-      <c r="AF43" s="27">
+      <c r="AF43" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C40</f>
         <v>-0.67019283771514904</v>
       </c>
-      <c r="AG43" s="27">
+      <c r="AG43" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B40</f>
         <v>3.4370362758636502E-2</v>
       </c>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A44" s="29"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="29"/>
-      <c r="J44" s="29"/>
-      <c r="K44" s="29"/>
-      <c r="L44" s="29"/>
-      <c r="M44" s="29"/>
-      <c r="N44" s="29"/>
-      <c r="O44" s="29"/>
-      <c r="P44" s="29"/>
-      <c r="Q44" s="29"/>
-      <c r="R44" s="29"/>
-      <c r="S44" s="29"/>
-      <c r="T44" s="29"/>
-      <c r="U44" s="30"/>
-      <c r="V44" s="30"/>
-      <c r="W44" s="30"/>
-      <c r="X44" s="30"/>
-      <c r="Y44" s="30"/>
-      <c r="Z44" s="30"/>
-      <c r="AB44" s="27">
+      <c r="A44" s="19"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="19"/>
+      <c r="M44" s="19"/>
+      <c r="N44" s="19"/>
+      <c r="O44" s="19"/>
+      <c r="P44" s="19"/>
+      <c r="Q44" s="19"/>
+      <c r="R44" s="19"/>
+      <c r="S44" s="19"/>
+      <c r="T44" s="19"/>
+      <c r="AB44" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G41</f>
         <v>-4.48850973043591E-4</v>
       </c>
-      <c r="AC44" s="27">
+      <c r="AC44" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F41</f>
         <v>-1.3324012979865101E-4</v>
       </c>
-      <c r="AD44" s="27">
+      <c r="AD44" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E41</f>
         <v>-3.5143312998115999E-3</v>
       </c>
-      <c r="AE44" s="27">
+      <c r="AE44" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D41</f>
         <v>-0.22372764348983801</v>
       </c>
-      <c r="AF44" s="27">
+      <c r="AF44" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C41</f>
         <v>-0.100444361567497</v>
       </c>
-      <c r="AG44" s="27">
+      <c r="AG44" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B41</f>
         <v>6.3757039606571198E-3</v>
       </c>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A45" s="29"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="29"/>
-      <c r="I45" s="29"/>
-      <c r="J45" s="29"/>
-      <c r="K45" s="29"/>
-      <c r="L45" s="29"/>
-      <c r="M45" s="29"/>
-      <c r="N45" s="29"/>
-      <c r="O45" s="29"/>
-      <c r="P45" s="29"/>
-      <c r="Q45" s="29"/>
-      <c r="R45" s="29"/>
-      <c r="S45" s="29"/>
-      <c r="T45" s="29"/>
-      <c r="U45" s="30"/>
-      <c r="V45" s="30"/>
-      <c r="W45" s="30"/>
-      <c r="X45" s="30"/>
-      <c r="Y45" s="30"/>
-      <c r="Z45" s="30"/>
-      <c r="AB45" s="27">
+      <c r="A45" s="19"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="19"/>
+      <c r="O45" s="19"/>
+      <c r="P45" s="19"/>
+      <c r="Q45" s="19"/>
+      <c r="R45" s="19"/>
+      <c r="S45" s="19"/>
+      <c r="T45" s="19"/>
+      <c r="AB45" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G42</f>
         <v>6.4870691858232E-4</v>
       </c>
-      <c r="AC45" s="27">
+      <c r="AC45" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F42</f>
         <v>-1.34663167409599E-3</v>
       </c>
-      <c r="AD45" s="27">
+      <c r="AD45" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E42</f>
         <v>8.9680150151252705E-2</v>
       </c>
-      <c r="AE45" s="27">
+      <c r="AE45" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D42</f>
         <v>-0.53976345062255904</v>
       </c>
-      <c r="AF45" s="27">
+      <c r="AF45" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C42</f>
         <v>0.378590047359467</v>
       </c>
-      <c r="AG45" s="27">
+      <c r="AG45" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B42</f>
         <v>1.5296399593353299E-2</v>
       </c>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A46" s="29"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="30"/>
-      <c r="V46" s="30"/>
-      <c r="W46" s="30"/>
-      <c r="X46" s="30"/>
-      <c r="Y46" s="30"/>
-      <c r="Z46" s="30"/>
-      <c r="AB46" s="27">
+      <c r="A46" s="19"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19"/>
+      <c r="K46" s="19"/>
+      <c r="L46" s="19"/>
+      <c r="M46" s="19"/>
+      <c r="N46" s="19"/>
+      <c r="O46" s="19"/>
+      <c r="P46" s="19"/>
+      <c r="Q46" s="19"/>
+      <c r="R46" s="19"/>
+      <c r="S46" s="19"/>
+      <c r="T46" s="19"/>
+      <c r="AB46" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G43</f>
         <v>-2.8338059782981899E-3</v>
       </c>
-      <c r="AC46" s="27">
+      <c r="AC46" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F43</f>
         <v>-3.8975423667579898E-3</v>
       </c>
-      <c r="AD46" s="27">
+      <c r="AD46" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E43</f>
         <v>-5.2740231156349203E-2</v>
       </c>
-      <c r="AE46" s="27">
+      <c r="AE46" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D43</f>
         <v>-0.73136901855468806</v>
       </c>
-      <c r="AF46" s="27">
+      <c r="AF46" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C43</f>
         <v>-0.64403772354125999</v>
       </c>
-      <c r="AG46" s="27">
+      <c r="AG46" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B43</f>
         <v>3.5194247961044298E-2</v>
       </c>
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A47" s="29"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="29"/>
-      <c r="K47" s="29"/>
-      <c r="L47" s="29"/>
-      <c r="M47" s="29"/>
-      <c r="N47" s="29"/>
-      <c r="O47" s="29"/>
-      <c r="P47" s="29"/>
-      <c r="Q47" s="29"/>
-      <c r="R47" s="29"/>
-      <c r="S47" s="29"/>
-      <c r="T47" s="29"/>
-      <c r="U47" s="30"/>
-      <c r="V47" s="30"/>
-      <c r="W47" s="30"/>
-      <c r="X47" s="30"/>
-      <c r="Y47" s="30"/>
-      <c r="Z47" s="30"/>
-      <c r="AB47" s="27">
+      <c r="A47" s="19"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="19"/>
+      <c r="K47" s="19"/>
+      <c r="L47" s="19"/>
+      <c r="M47" s="19"/>
+      <c r="N47" s="19"/>
+      <c r="O47" s="19"/>
+      <c r="P47" s="19"/>
+      <c r="Q47" s="19"/>
+      <c r="R47" s="19"/>
+      <c r="S47" s="19"/>
+      <c r="T47" s="19"/>
+      <c r="AB47" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G44</f>
         <v>-2.4467429611831899E-3</v>
       </c>
-      <c r="AC47" s="27">
+      <c r="AC47" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F44</f>
         <v>-3.9606718346476598E-3</v>
       </c>
-      <c r="AD47" s="27">
+      <c r="AD47" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E44</f>
         <v>-6.55845552682877E-2</v>
       </c>
-      <c r="AE47" s="27">
+      <c r="AE47" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D44</f>
         <v>-1.3344798088073699</v>
       </c>
-      <c r="AF47" s="27">
+      <c r="AF47" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C44</f>
         <v>-0.42153304815292397</v>
       </c>
-      <c r="AG47" s="27">
+      <c r="AG47" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B44</f>
         <v>3.0811607837676998E-2</v>
       </c>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A48" s="29"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-      <c r="L48" s="29"/>
-      <c r="M48" s="29"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="29"/>
-      <c r="S48" s="29"/>
-      <c r="T48" s="29"/>
-      <c r="U48" s="30"/>
-      <c r="V48" s="30"/>
-      <c r="W48" s="30"/>
-      <c r="X48" s="30"/>
-      <c r="Y48" s="30"/>
-      <c r="Z48" s="30"/>
-      <c r="AB48" s="27">
+      <c r="A48" s="19"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="19"/>
+      <c r="K48" s="19"/>
+      <c r="L48" s="19"/>
+      <c r="M48" s="19"/>
+      <c r="N48" s="19"/>
+      <c r="O48" s="19"/>
+      <c r="P48" s="19"/>
+      <c r="Q48" s="19"/>
+      <c r="R48" s="19"/>
+      <c r="S48" s="19"/>
+      <c r="T48" s="19"/>
+      <c r="AB48" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G45</f>
         <v>-2.2109632845967999E-3</v>
       </c>
-      <c r="AC48" s="27">
+      <c r="AC48" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F45</f>
         <v>-1.3992630410939501E-3</v>
       </c>
-      <c r="AD48" s="27">
+      <c r="AD48" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E45</f>
         <v>-7.3739819228649098E-2</v>
       </c>
-      <c r="AE48" s="27">
+      <c r="AE48" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D45</f>
         <v>-0.77465367317199696</v>
       </c>
-      <c r="AF48" s="27">
+      <c r="AF48" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C45</f>
         <v>-0.54947280883789096</v>
       </c>
-      <c r="AG48" s="27">
+      <c r="AG48" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B45</f>
         <v>3.94041240215302E-2</v>
       </c>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A49" s="29"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="29"/>
-      <c r="R49" s="29"/>
-      <c r="S49" s="29"/>
-      <c r="T49" s="29"/>
-      <c r="U49" s="30"/>
-      <c r="V49" s="30"/>
-      <c r="W49" s="30"/>
-      <c r="X49" s="30"/>
-      <c r="Y49" s="30"/>
-      <c r="Z49" s="30"/>
-      <c r="AB49" s="27">
+      <c r="A49" s="19"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="19"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="19"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="19"/>
+      <c r="O49" s="19"/>
+      <c r="P49" s="19"/>
+      <c r="Q49" s="19"/>
+      <c r="R49" s="19"/>
+      <c r="S49" s="19"/>
+      <c r="T49" s="19"/>
+      <c r="AB49" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G46</f>
         <v>0</v>
       </c>
-      <c r="AC49" s="27">
+      <c r="AC49" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F46</f>
         <v>0</v>
       </c>
-      <c r="AD49" s="27">
+      <c r="AD49" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E46</f>
         <v>0</v>
       </c>
-      <c r="AE49" s="27">
+      <c r="AE49" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D46</f>
         <v>0</v>
       </c>
-      <c r="AF49" s="27">
+      <c r="AF49" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C46</f>
         <v>0</v>
       </c>
-      <c r="AG49" s="27">
+      <c r="AG49" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B46</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A50" s="29"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
-      <c r="E50" s="29"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="29"/>
-      <c r="I50" s="29"/>
-      <c r="J50" s="29"/>
-      <c r="K50" s="29"/>
-      <c r="L50" s="29"/>
-      <c r="M50" s="29"/>
-      <c r="N50" s="29"/>
-      <c r="O50" s="29"/>
-      <c r="P50" s="29"/>
-      <c r="Q50" s="29"/>
-      <c r="R50" s="29"/>
-      <c r="S50" s="29"/>
-      <c r="T50" s="29"/>
-      <c r="U50" s="30"/>
-      <c r="V50" s="30"/>
-      <c r="W50" s="30"/>
-      <c r="X50" s="30"/>
-      <c r="Y50" s="30"/>
-      <c r="Z50" s="30"/>
-      <c r="AB50" s="27">
+      <c r="A50" s="19"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="19"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="19"/>
+      <c r="K50" s="19"/>
+      <c r="L50" s="19"/>
+      <c r="M50" s="19"/>
+      <c r="N50" s="19"/>
+      <c r="O50" s="19"/>
+      <c r="P50" s="19"/>
+      <c r="Q50" s="19"/>
+      <c r="R50" s="19"/>
+      <c r="S50" s="19"/>
+      <c r="T50" s="19"/>
+      <c r="AB50" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G47</f>
         <v>0</v>
       </c>
-      <c r="AC50" s="27">
+      <c r="AC50" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F47</f>
         <v>0</v>
       </c>
-      <c r="AD50" s="27">
+      <c r="AD50" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E47</f>
         <v>0</v>
       </c>
-      <c r="AE50" s="27">
+      <c r="AE50" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D47</f>
         <v>0</v>
       </c>
-      <c r="AF50" s="27">
+      <c r="AF50" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C47</f>
         <v>0</v>
       </c>
-      <c r="AG50" s="27">
+      <c r="AG50" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B47</f>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A51" s="29"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="29"/>
-      <c r="I51" s="29"/>
-      <c r="J51" s="29"/>
-      <c r="K51" s="29"/>
-      <c r="L51" s="29"/>
-      <c r="M51" s="29"/>
-      <c r="N51" s="29"/>
-      <c r="O51" s="29"/>
-      <c r="P51" s="29"/>
-      <c r="Q51" s="29"/>
-      <c r="R51" s="29"/>
-      <c r="S51" s="29"/>
-      <c r="T51" s="29"/>
-      <c r="U51" s="30"/>
-      <c r="V51" s="30"/>
-      <c r="W51" s="30"/>
-      <c r="X51" s="30"/>
-      <c r="Y51" s="30"/>
-      <c r="Z51" s="30"/>
-      <c r="AB51" s="27">
+      <c r="A51" s="19"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="19"/>
+      <c r="K51" s="19"/>
+      <c r="L51" s="19"/>
+      <c r="M51" s="19"/>
+      <c r="N51" s="19"/>
+      <c r="O51" s="19"/>
+      <c r="P51" s="19"/>
+      <c r="Q51" s="19"/>
+      <c r="R51" s="19"/>
+      <c r="S51" s="19"/>
+      <c r="T51" s="19"/>
+      <c r="AB51" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G48</f>
         <v>0</v>
       </c>
-      <c r="AC51" s="27">
+      <c r="AC51" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F48</f>
         <v>0</v>
       </c>
-      <c r="AD51" s="27">
+      <c r="AD51" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E48</f>
         <v>0</v>
       </c>
-      <c r="AE51" s="27">
+      <c r="AE51" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D48</f>
         <v>0</v>
       </c>
-      <c r="AF51" s="27">
+      <c r="AF51" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C48</f>
         <v>0</v>
       </c>
-      <c r="AG51" s="27">
+      <c r="AG51" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B48</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A52" s="29"/>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="29"/>
-      <c r="P52" s="29"/>
-      <c r="Q52" s="29"/>
-      <c r="R52" s="29"/>
-      <c r="S52" s="29"/>
-      <c r="T52" s="29"/>
-      <c r="U52" s="30"/>
-      <c r="V52" s="30"/>
-      <c r="W52" s="30"/>
-      <c r="X52" s="30"/>
-      <c r="Y52" s="30"/>
-      <c r="Z52" s="30"/>
-      <c r="AB52" s="27">
+      <c r="A52" s="19"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="19"/>
+      <c r="L52" s="19"/>
+      <c r="M52" s="19"/>
+      <c r="N52" s="19"/>
+      <c r="O52" s="19"/>
+      <c r="P52" s="19"/>
+      <c r="Q52" s="19"/>
+      <c r="R52" s="19"/>
+      <c r="S52" s="19"/>
+      <c r="T52" s="19"/>
+      <c r="AB52" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$G49</f>
         <v>0</v>
       </c>
-      <c r="AC52" s="27">
+      <c r="AC52" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$F49</f>
         <v>0</v>
       </c>
-      <c r="AD52" s="27">
+      <c r="AD52" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$E49</f>
         <v>0</v>
       </c>
-      <c r="AE52" s="27">
+      <c r="AE52" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$D49</f>
         <v>0</v>
       </c>
-      <c r="AF52" s="27">
+      <c r="AF52" s="17">
         <f>-1*'[1]ATI_Sensor_Log(2.0to1.0)'!$C49</f>
         <v>0</v>
       </c>
-      <c r="AG52" s="27">
+      <c r="AG52" s="17">
         <f>'[1]ATI_Sensor_Log(2.0to1.0)'!$B49</f>
         <v>0</v>
       </c>
@@ -7095,155 +7046,155 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3993EB2-5DD9-4DA0-BCDE-0457543667A5}">
-  <dimension ref="A1:AE52"/>
+  <dimension ref="A1:AE54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="22" width="9" style="4"/>
-    <col min="23" max="23" width="32" style="4" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="4"/>
+    <col min="1" max="22" width="9" style="3"/>
+    <col min="23" max="23" width="32" style="3" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
+      <c r="A1" s="27"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="7" t="s">
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="32" t="s">
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="34" t="s">
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="36" t="s">
+      <c r="T2" s="42"/>
+      <c r="U2" s="42"/>
+      <c r="V2" s="42"/>
+      <c r="W2" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="37"/>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="37"/>
-      <c r="AE2" s="37"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="43"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43"/>
+      <c r="AE2" s="43"/>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="K3" s="17" t="s">
+      <c r="J3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="17" t="s">
+      <c r="L3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="M3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="20" t="s">
+      <c r="N3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="O3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="P3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="17" t="s">
+      <c r="Q3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="R3" s="22" t="s">
+      <c r="R3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="S3" s="20" t="s">
+      <c r="S3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="T3" s="17" t="s">
+      <c r="T3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="U3" s="17" t="s">
+      <c r="U3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="V3" s="17" t="s">
+      <c r="V3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="W3" s="38"/>
-      <c r="X3" s="12"/>
-      <c r="Y3" s="12"/>
-      <c r="Z3" s="12"/>
-      <c r="AA3" s="12"/>
-      <c r="AB3" s="12"/>
-      <c r="AC3" s="12"/>
-      <c r="AD3" s="12"/>
-      <c r="AE3" s="12"/>
+      <c r="W3" s="45"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="5"/>
+      <c r="AD3" s="5"/>
+      <c r="AE3" s="5"/>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -7270,66 +7221,66 @@
         <f>'get_proximal_value Validation'!F4</f>
         <v>0.30399999999999999</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="18">
         <f>'get_proximal_value Validation'!G4</f>
         <v>-9.1163394972681999E-4</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="18">
         <f>'get_proximal_value Validation'!H4</f>
         <v>-1.0851300321519401E-3</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="18">
         <f>'get_proximal_value Validation'!I4</f>
         <v>-2.5136896874755599E-3</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="18">
         <f>'get_proximal_value Validation'!J4</f>
         <v>-0.19703710079193101</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="18">
         <f>'get_proximal_value Validation'!K4</f>
         <v>-0.12924839556217199</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="18">
         <f>'get_proximal_value Validation'!L4</f>
         <v>8.4088072180748003E-3</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="18">
         <f>'get_proximal_value Validation'!M4</f>
         <v>0.30399999999999999</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="18">
         <v>0.1552202006</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="18">
         <v>7.1353470500000002E-2</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="18">
         <v>3.9434929399999999E-2</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="18">
         <v>-0.97199647789999999</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="18">
         <v>0.30399999999999999</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="18">
         <f>N4-A4</f>
         <v>1.3390440599999998E-2</v>
       </c>
-      <c r="T4" s="28">
+      <c r="T4" s="18">
         <f>O4-B4</f>
         <v>-6.7072949999999465E-4</v>
       </c>
-      <c r="U4" s="28">
+      <c r="U4" s="18">
         <f>P4-C4</f>
         <v>3.9434929399999999E-2</v>
       </c>
-      <c r="V4" s="28">
+      <c r="V4" s="18">
         <f>Q4-D4</f>
         <v>-6.0251567899999969E-2</v>
       </c>
-      <c r="W4" s="39">
+      <c r="W4" s="13">
         <f>SUM(S4:V4)^2</f>
         <v>6.5560233320870236E-5</v>
       </c>
@@ -7359,67 +7310,67 @@
         <f>'get_proximal_value Validation'!F5</f>
         <v>0.378</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="18">
         <f>'get_proximal_value Validation'!G5</f>
         <v>5.73261640965939E-4</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="18">
         <f>'get_proximal_value Validation'!H5</f>
         <v>-8.4196426905691602E-4</v>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="18">
         <f>'get_proximal_value Validation'!I5</f>
         <v>7.2134017944335896E-2</v>
       </c>
-      <c r="J5" s="28">
+      <c r="J5" s="18">
         <f>'get_proximal_value Validation'!J5</f>
         <v>-0.55127584934234597</v>
       </c>
-      <c r="K5" s="28">
+      <c r="K5" s="18">
         <f>'get_proximal_value Validation'!K5</f>
         <v>0.51616352796554599</v>
       </c>
-      <c r="L5" s="28">
+      <c r="L5" s="18">
         <f>'get_proximal_value Validation'!L5</f>
         <v>1.7094016075134302E-2</v>
       </c>
-      <c r="M5" s="28">
+      <c r="M5" s="18">
         <f>'get_proximal_value Validation'!M5</f>
         <v>0.378</v>
       </c>
-      <c r="N5" s="28">
+      <c r="N5" s="18">
         <v>0.55294679660000001</v>
       </c>
-      <c r="O5" s="28">
+      <c r="O5" s="18">
         <v>0.104934607</v>
       </c>
-      <c r="P5" s="28">
+      <c r="P5" s="18">
         <v>2.65311474E-2</v>
       </c>
-      <c r="Q5" s="28">
+      <c r="Q5" s="18">
         <v>1.7006166752</v>
       </c>
-      <c r="R5" s="28">
+      <c r="R5" s="18">
         <v>0.378</v>
       </c>
-      <c r="S5" s="28">
+      <c r="S5" s="18">
         <f t="shared" ref="S5:S23" si="0">N5-A5</f>
         <v>-5.4511573400000013E-2</v>
       </c>
-      <c r="T5" s="28">
+      <c r="T5" s="18">
         <f t="shared" ref="T5:T23" si="1">O5-B5</f>
         <v>7.8702370000000021E-3</v>
       </c>
-      <c r="U5" s="28">
+      <c r="U5" s="18">
         <f t="shared" ref="U5:U23" si="2">P5-C5</f>
         <v>2.65311474E-2</v>
       </c>
-      <c r="V5" s="28">
+      <c r="V5" s="18">
         <f t="shared" ref="V5:V23" si="3">Q5-D5</f>
         <v>-5.1823494800000036E-2</v>
       </c>
-      <c r="W5" s="39">
-        <f t="shared" ref="W5:W40" si="4">SUM(S5:V5)^2</f>
+      <c r="W5" s="13">
+        <f t="shared" ref="W5:W23" si="4">SUM(S5:V5)^2</f>
         <v>5.1744548650383901E-3</v>
       </c>
     </row>
@@ -7448,66 +7399,66 @@
         <f>'get_proximal_value Validation'!F6</f>
         <v>0.61699999999999999</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="18">
         <f>'get_proximal_value Validation'!G6</f>
         <v>-2.39273207262158E-3</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="18">
         <f>'get_proximal_value Validation'!H6</f>
         <v>-3.4488118253648298E-3</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="18">
         <f>'get_proximal_value Validation'!I6</f>
         <v>-2.6666743680834801E-2</v>
       </c>
-      <c r="J6" s="28">
+      <c r="J6" s="18">
         <f>'get_proximal_value Validation'!J6</f>
         <v>-2.8852019459009198E-2</v>
       </c>
-      <c r="K6" s="28">
+      <c r="K6" s="18">
         <f>'get_proximal_value Validation'!K6</f>
         <v>-0.67019283771514904</v>
       </c>
-      <c r="L6" s="28">
+      <c r="L6" s="18">
         <f>'get_proximal_value Validation'!L6</f>
         <v>3.4370362758636502E-2</v>
       </c>
-      <c r="M6" s="28">
+      <c r="M6" s="18">
         <f>'get_proximal_value Validation'!M6</f>
         <v>0.61699999999999999</v>
       </c>
-      <c r="N6" s="28">
+      <c r="N6" s="18">
         <v>0.87128265559999996</v>
       </c>
-      <c r="O6" s="28">
+      <c r="O6" s="18">
         <v>5.4308711599999997E-2</v>
       </c>
-      <c r="P6" s="28">
+      <c r="P6" s="18">
         <v>3.3026537799999998E-2</v>
       </c>
-      <c r="Q6" s="28">
+      <c r="Q6" s="18">
         <v>-0.87068177329999996</v>
       </c>
-      <c r="R6" s="28">
+      <c r="R6" s="18">
         <v>0.61699999999999999</v>
       </c>
-      <c r="S6" s="28">
+      <c r="S6" s="18">
         <f t="shared" si="0"/>
         <v>-1.2373184400000015E-2</v>
       </c>
-      <c r="T6" s="28">
+      <c r="T6" s="18">
         <f t="shared" si="1"/>
         <v>2.9999159999999359E-4</v>
       </c>
-      <c r="U6" s="28">
+      <c r="U6" s="18">
         <f t="shared" si="2"/>
         <v>3.3026537799999998E-2</v>
       </c>
-      <c r="V6" s="28">
+      <c r="V6" s="18">
         <f t="shared" si="3"/>
         <v>4.0934306700000089E-2</v>
       </c>
-      <c r="W6" s="39">
+      <c r="W6" s="13">
         <f t="shared" si="4"/>
         <v>3.830081432940521E-3</v>
       </c>
@@ -7537,66 +7488,66 @@
         <f>'get_proximal_value Validation'!F7</f>
         <v>0.21</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="18">
         <f>'get_proximal_value Validation'!G7</f>
         <v>-4.48850973043591E-4</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="18">
         <f>'get_proximal_value Validation'!H7</f>
         <v>-1.3324012979865101E-4</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="18">
         <f>'get_proximal_value Validation'!I7</f>
         <v>-3.5143312998115999E-3</v>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="18">
         <f>'get_proximal_value Validation'!J7</f>
         <v>-0.22372764348983801</v>
       </c>
-      <c r="K7" s="28">
+      <c r="K7" s="18">
         <f>'get_proximal_value Validation'!K7</f>
         <v>-0.100444361567497</v>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="18">
         <f>'get_proximal_value Validation'!L7</f>
         <v>6.3757039606571198E-3</v>
       </c>
-      <c r="M7" s="28">
+      <c r="M7" s="18">
         <f>'get_proximal_value Validation'!M7</f>
         <v>0.21</v>
       </c>
-      <c r="N7" s="28">
+      <c r="N7" s="18">
         <v>0.10168109409999999</v>
       </c>
-      <c r="O7" s="28">
+      <c r="O7" s="18">
         <v>8.0464167399999995E-2</v>
       </c>
-      <c r="P7" s="28">
+      <c r="P7" s="18">
         <v>4.7018612699999997E-2</v>
       </c>
-      <c r="Q7" s="28">
+      <c r="Q7" s="18">
         <v>-1.8110141503999999</v>
       </c>
-      <c r="R7" s="28">
+      <c r="R7" s="18">
         <v>0.21</v>
       </c>
-      <c r="S7" s="28">
+      <c r="S7" s="18">
         <f t="shared" si="0"/>
         <v>9.1550341000000007E-3</v>
       </c>
-      <c r="T7" s="28">
+      <c r="T7" s="18">
         <f t="shared" si="1"/>
         <v>4.1528373999999979E-3</v>
       </c>
-      <c r="U7" s="28">
+      <c r="U7" s="18">
         <f t="shared" si="2"/>
         <v>4.7018612699999997E-2</v>
       </c>
-      <c r="V7" s="28">
+      <c r="V7" s="18">
         <f t="shared" si="3"/>
         <v>-1.0194470399999878E-2</v>
       </c>
-      <c r="W7" s="39">
+      <c r="W7" s="13">
         <f t="shared" si="4"/>
         <v>2.5132188076434025E-3</v>
       </c>
@@ -7626,66 +7577,66 @@
         <f>'get_proximal_value Validation'!F8</f>
         <v>0.43</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="18">
         <f>'get_proximal_value Validation'!G8</f>
         <v>3.9714667946100202E-4</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="18">
         <f>'get_proximal_value Validation'!H8</f>
         <v>-8.1160559784621E-4</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="18">
         <f>'get_proximal_value Validation'!I8</f>
         <v>4.53379787504673E-2</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="18">
         <f>'get_proximal_value Validation'!J8</f>
         <v>-0.44326165318489102</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="18">
         <f>'get_proximal_value Validation'!K8</f>
         <v>0.24324490129947701</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="18">
         <f>'get_proximal_value Validation'!L8</f>
         <v>1.42691433429718E-2</v>
       </c>
-      <c r="M8" s="28">
+      <c r="M8" s="18">
         <f>'get_proximal_value Validation'!M8</f>
         <v>0.43</v>
       </c>
-      <c r="N8" s="28">
+      <c r="N8" s="18">
         <v>0.24965928770000001</v>
       </c>
-      <c r="O8" s="28">
+      <c r="O8" s="18">
         <v>0.12562618119999999</v>
       </c>
-      <c r="P8" s="28">
+      <c r="P8" s="18">
         <v>4.3942473199999998E-2</v>
       </c>
-      <c r="Q8" s="28">
+      <c r="Q8" s="18">
         <v>1.4859877639000001</v>
       </c>
-      <c r="R8" s="28">
+      <c r="R8" s="18">
         <v>0.43</v>
       </c>
-      <c r="S8" s="28">
+      <c r="S8" s="18">
         <f t="shared" si="0"/>
         <v>-1.6165532300000007E-2</v>
       </c>
-      <c r="T8" s="28">
+      <c r="T8" s="18">
         <f t="shared" si="1"/>
         <v>9.8649111999999928E-3</v>
       </c>
-      <c r="U8" s="28">
+      <c r="U8" s="18">
         <f t="shared" si="2"/>
         <v>4.3942473199999998E-2</v>
       </c>
-      <c r="V8" s="28">
+      <c r="V8" s="18">
         <f t="shared" si="3"/>
         <v>-0.14289624609999985</v>
       </c>
-      <c r="W8" s="39">
+      <c r="W8" s="13">
         <f t="shared" si="4"/>
         <v>1.1078487456307207E-2</v>
       </c>
@@ -7715,66 +7666,66 @@
         <f>'get_proximal_value Validation'!F9</f>
         <v>0.76800000000000002</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="18">
         <f>'get_proximal_value Validation'!G9</f>
         <v>-2.8824871405959099E-3</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="18">
         <f>'get_proximal_value Validation'!H9</f>
         <v>-2.6444175746291902E-3</v>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="18">
         <f>'get_proximal_value Validation'!I9</f>
         <v>-5.5171221494674703E-2</v>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="18">
         <f>'get_proximal_value Validation'!J9</f>
         <v>-0.967154741287231</v>
       </c>
-      <c r="K9" s="28">
+      <c r="K9" s="18">
         <f>'get_proximal_value Validation'!K9</f>
         <v>-0.338964402675629</v>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="18">
         <f>'get_proximal_value Validation'!L9</f>
         <v>4.3315857648849501E-2</v>
       </c>
-      <c r="M9" s="28">
+      <c r="M9" s="18">
         <f>'get_proximal_value Validation'!M9</f>
         <v>0.76800000000000002</v>
       </c>
-      <c r="N9" s="28">
+      <c r="N9" s="18">
         <v>0.40711206760000002</v>
       </c>
-      <c r="O9" s="28">
+      <c r="O9" s="18">
         <v>0.2</v>
       </c>
-      <c r="P9" s="28">
+      <c r="P9" s="18">
         <v>0.120810722</v>
       </c>
-      <c r="Q9" s="28">
+      <c r="Q9" s="18">
         <v>-2.1884713775</v>
       </c>
-      <c r="R9" s="28">
+      <c r="R9" s="18">
         <v>0.76800000000000002</v>
       </c>
-      <c r="S9" s="28">
+      <c r="S9" s="18">
         <f t="shared" si="0"/>
         <v>-4.2887932399999995E-2</v>
       </c>
-      <c r="T9" s="28">
+      <c r="T9" s="18">
         <f t="shared" si="1"/>
         <v>2.6267010000000007E-2</v>
       </c>
-      <c r="U9" s="28">
+      <c r="U9" s="18">
         <f t="shared" si="2"/>
         <v>0.120810722</v>
       </c>
-      <c r="V9" s="28">
+      <c r="V9" s="18">
         <f t="shared" si="3"/>
         <v>-0.17993850750000018</v>
       </c>
-      <c r="W9" s="39">
+      <c r="W9" s="13">
         <f t="shared" si="4"/>
         <v>5.7378667485195479E-3</v>
       </c>
@@ -7804,66 +7755,66 @@
         <f>'get_proximal_value Validation'!F10</f>
         <v>0.497</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="18">
         <f>'get_proximal_value Validation'!G10</f>
         <v>-1.4106486923992599E-3</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="18">
         <f>'get_proximal_value Validation'!H10</f>
         <v>-2.5641322135925302E-3</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="18">
         <f>'get_proximal_value Validation'!I10</f>
         <v>-1.1485542170703401E-2</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="18">
         <f>'get_proximal_value Validation'!J10</f>
         <v>-0.36418968439102201</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="18">
         <f>'get_proximal_value Validation'!K10</f>
         <v>-0.149911478161812</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="18">
         <f>'get_proximal_value Validation'!L10</f>
         <v>2.13295146822929E-2</v>
       </c>
-      <c r="M10" s="28">
+      <c r="M10" s="18">
         <f>'get_proximal_value Validation'!M10</f>
         <v>0.497</v>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="18">
         <v>0.18504490430000001</v>
       </c>
-      <c r="O10" s="28">
+      <c r="O10" s="18">
         <v>0.1587055268</v>
       </c>
-      <c r="P10" s="28">
+      <c r="P10" s="18">
         <v>8.6093611799999997E-2</v>
       </c>
-      <c r="Q10" s="28">
+      <c r="Q10" s="18">
         <v>-0.99703021329999997</v>
       </c>
-      <c r="R10" s="28">
+      <c r="R10" s="18">
         <v>0.497</v>
       </c>
-      <c r="S10" s="28">
+      <c r="S10" s="18">
         <f t="shared" si="0"/>
         <v>9.6436943000000053E-3</v>
       </c>
-      <c r="T10" s="28">
+      <c r="T10" s="18">
         <f t="shared" si="1"/>
         <v>1.4887496799999983E-2</v>
       </c>
-      <c r="U10" s="28">
+      <c r="U10" s="18">
         <f t="shared" si="2"/>
         <v>8.6093611799999997E-2</v>
       </c>
-      <c r="V10" s="28">
+      <c r="V10" s="18">
         <f t="shared" si="3"/>
         <v>0.11481006670000005</v>
       </c>
-      <c r="W10" s="39">
+      <c r="W10" s="13">
         <f t="shared" si="4"/>
         <v>5.0820880431569015E-2</v>
       </c>
@@ -7893,66 +7844,66 @@
         <f>'get_proximal_value Validation'!F11</f>
         <v>0.23</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="18">
         <f>'get_proximal_value Validation'!G11</f>
         <v>-2.0074252970516699E-3</v>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="18">
         <f>'get_proximal_value Validation'!H11</f>
         <v>-4.5337807387113598E-4</v>
       </c>
-      <c r="I11" s="28">
+      <c r="I11" s="18">
         <f>'get_proximal_value Validation'!I11</f>
         <v>-7.8970164060592707E-2</v>
       </c>
-      <c r="J11" s="28">
+      <c r="J11" s="18">
         <f>'get_proximal_value Validation'!J11</f>
         <v>-0.77051401138305697</v>
       </c>
-      <c r="K11" s="28">
+      <c r="K11" s="18">
         <f>'get_proximal_value Validation'!K11</f>
         <v>-0.66304510831832897</v>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="18">
         <f>'get_proximal_value Validation'!L11</f>
         <v>4.46887910366058E-2</v>
       </c>
-      <c r="M11" s="28">
+      <c r="M11" s="18">
         <f>'get_proximal_value Validation'!M11</f>
         <v>0.23</v>
       </c>
-      <c r="N11" s="28">
+      <c r="N11" s="18">
         <v>0.86172972640000001</v>
       </c>
-      <c r="O11" s="28">
+      <c r="O11" s="18">
         <v>0.1078973567</v>
       </c>
-      <c r="P11" s="28">
+      <c r="P11" s="18">
         <v>5.71078364E-2</v>
       </c>
-      <c r="Q11" s="28">
+      <c r="Q11" s="18">
         <v>-2.0893219276999999</v>
       </c>
-      <c r="R11" s="28">
+      <c r="R11" s="18">
         <v>0.23</v>
       </c>
-      <c r="S11" s="28">
+      <c r="S11" s="18">
         <f t="shared" si="0"/>
         <v>-4.9653503599999982E-2</v>
       </c>
-      <c r="T11" s="28">
+      <c r="T11" s="18">
         <f t="shared" si="1"/>
         <v>4.6300867000000079E-3</v>
       </c>
-      <c r="U11" s="28">
+      <c r="U11" s="18">
         <f t="shared" si="2"/>
         <v>5.71078364E-2</v>
       </c>
-      <c r="V11" s="28">
+      <c r="V11" s="18">
         <f t="shared" si="3"/>
         <v>1.5847852300000298E-2</v>
       </c>
-      <c r="W11" s="39">
+      <c r="W11" s="13">
         <f t="shared" si="4"/>
         <v>7.8021180790909341E-4</v>
       </c>
@@ -7982,66 +7933,66 @@
         <f>'get_proximal_value Validation'!F12</f>
         <v>0</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="18">
         <f>'get_proximal_value Validation'!G12</f>
         <v>6.4870691858232E-4</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="18">
         <f>'get_proximal_value Validation'!H12</f>
         <v>-1.34663167409599E-3</v>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="18">
         <f>'get_proximal_value Validation'!I12</f>
         <v>8.9680150151252705E-2</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="18">
         <f>'get_proximal_value Validation'!J12</f>
         <v>-0.53976345062255904</v>
       </c>
-      <c r="K12" s="28">
+      <c r="K12" s="18">
         <f>'get_proximal_value Validation'!K12</f>
         <v>0.378590047359467</v>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="18">
         <f>'get_proximal_value Validation'!L12</f>
         <v>1.5296399593353299E-2</v>
       </c>
-      <c r="M12" s="28">
+      <c r="M12" s="18">
         <f>'get_proximal_value Validation'!M12</f>
         <v>0</v>
       </c>
-      <c r="N12" s="28">
+      <c r="N12" s="18">
         <v>0.65954870119999998</v>
       </c>
-      <c r="O12" s="28">
+      <c r="O12" s="18">
         <v>0.16738955480000001</v>
       </c>
-      <c r="P12" s="28">
+      <c r="P12" s="18">
         <v>3.6041738300000001E-2</v>
       </c>
-      <c r="Q12" s="28">
+      <c r="Q12" s="18">
         <v>1.9652106119999999</v>
       </c>
-      <c r="R12" s="28">
-        <v>0</v>
-      </c>
-      <c r="S12" s="28">
+      <c r="R12" s="18">
+        <v>0</v>
+      </c>
+      <c r="S12" s="18">
         <f t="shared" si="0"/>
         <v>-1.3668048800000054E-2</v>
       </c>
-      <c r="T12" s="28">
+      <c r="T12" s="18">
         <f t="shared" si="1"/>
         <v>1.0806224800000014E-2</v>
       </c>
-      <c r="U12" s="28">
+      <c r="U12" s="18">
         <f t="shared" si="2"/>
         <v>3.6041738300000001E-2</v>
       </c>
-      <c r="V12" s="28">
+      <c r="V12" s="18">
         <f t="shared" si="3"/>
         <v>-1.9868268000000189E-2</v>
       </c>
-      <c r="W12" s="39">
+      <c r="W12" s="13">
         <f t="shared" si="4"/>
         <v>1.7719992721629759E-4</v>
       </c>
@@ -8071,66 +8022,66 @@
         <f>'get_proximal_value Validation'!F13</f>
         <v>0</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="18">
         <f>'get_proximal_value Validation'!G13</f>
         <v>2.1531186066567902E-3</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="18">
         <f>'get_proximal_value Validation'!H13</f>
         <v>-1.85897364281118E-3</v>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="18">
         <f>'get_proximal_value Validation'!I13</f>
         <v>7.3820367455482497E-2</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="18">
         <f>'get_proximal_value Validation'!J13</f>
         <v>-0.43470159173011802</v>
       </c>
-      <c r="K13" s="28">
+      <c r="K13" s="18">
         <f>'get_proximal_value Validation'!K13</f>
         <v>0.22742748260498</v>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="18">
         <f>'get_proximal_value Validation'!L13</f>
         <v>3.35876196622849E-2</v>
       </c>
-      <c r="M13" s="28">
+      <c r="M13" s="18">
         <f>'get_proximal_value Validation'!M13</f>
         <v>0</v>
       </c>
-      <c r="N13" s="28">
+      <c r="N13" s="18">
         <v>0.49264697829999998</v>
       </c>
-      <c r="O13" s="28">
+      <c r="O13" s="18">
         <v>0.2</v>
       </c>
-      <c r="P13" s="28">
+      <c r="P13" s="18">
         <v>0.1214923366</v>
       </c>
-      <c r="Q13" s="28">
+      <c r="Q13" s="18">
         <v>2.0402252147</v>
       </c>
-      <c r="R13" s="28">
-        <v>0</v>
-      </c>
-      <c r="S13" s="28">
+      <c r="R13" s="18">
+        <v>0</v>
+      </c>
+      <c r="S13" s="18">
         <f t="shared" si="0"/>
         <v>-2.0642681699999998E-2</v>
       </c>
-      <c r="T13" s="28">
+      <c r="T13" s="18">
         <f t="shared" si="1"/>
         <v>1.158126000000001E-2</v>
       </c>
-      <c r="U13" s="28">
+      <c r="U13" s="18">
         <f t="shared" si="2"/>
         <v>0.1214923366</v>
       </c>
-      <c r="V13" s="28">
+      <c r="V13" s="18">
         <f t="shared" si="3"/>
         <v>8.8863524700000029E-2</v>
       </c>
-      <c r="W13" s="39">
+      <c r="W13" s="13">
         <f t="shared" si="4"/>
         <v>4.0519451413878062E-2</v>
       </c>
@@ -8160,66 +8111,66 @@
         <f>'get_proximal_value Validation'!F14</f>
         <v>0.76800000000000002</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="18">
         <f>'get_proximal_value Validation'!G14</f>
         <v>-1.50931708049029E-3</v>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="18">
         <f>'get_proximal_value Validation'!H14</f>
         <v>-2.2329168859869198E-3</v>
       </c>
-      <c r="I14" s="28">
+      <c r="I14" s="18">
         <f>'get_proximal_value Validation'!I14</f>
         <v>-5.9763666242361103E-2</v>
       </c>
-      <c r="J14" s="28">
+      <c r="J14" s="18">
         <f>'get_proximal_value Validation'!J14</f>
         <v>-0.94436967372894298</v>
       </c>
-      <c r="K14" s="28">
+      <c r="K14" s="18">
         <f>'get_proximal_value Validation'!K14</f>
         <v>-0.32222291827201799</v>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="18">
         <f>'get_proximal_value Validation'!L14</f>
         <v>2.7182862162589999E-2</v>
       </c>
-      <c r="M14" s="28">
+      <c r="M14" s="18">
         <f>'get_proximal_value Validation'!M14</f>
         <v>0.76800000000000002</v>
       </c>
-      <c r="N14" s="28">
+      <c r="N14" s="18">
         <v>0.38119508289999998</v>
       </c>
-      <c r="O14" s="28">
+      <c r="O14" s="18">
         <v>0.2</v>
       </c>
-      <c r="P14" s="28">
+      <c r="P14" s="18">
         <v>7.2169630799999995E-2</v>
       </c>
-      <c r="Q14" s="28">
+      <c r="Q14" s="18">
         <v>-2.2004415011999998</v>
       </c>
-      <c r="R14" s="28">
+      <c r="R14" s="18">
         <v>0.76800000000000002</v>
       </c>
-      <c r="S14" s="28">
+      <c r="S14" s="18">
         <f t="shared" si="0"/>
         <v>-3.7825917099999995E-2</v>
       </c>
-      <c r="T14" s="28">
+      <c r="T14" s="18">
         <f t="shared" si="1"/>
         <v>6.7813300000000021E-3</v>
       </c>
-      <c r="U14" s="28">
+      <c r="U14" s="18">
         <f t="shared" si="2"/>
         <v>7.2169630799999995E-2</v>
       </c>
-      <c r="V14" s="28">
+      <c r="V14" s="18">
         <f t="shared" si="3"/>
         <v>-0.25515282119999982</v>
       </c>
-      <c r="W14" s="39">
+      <c r="W14" s="13">
         <f t="shared" si="4"/>
         <v>4.580788954158943E-2</v>
       </c>
@@ -8249,66 +8200,66 @@
         <f>'get_proximal_value Validation'!F15</f>
         <v>0.1</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="18">
         <f>'get_proximal_value Validation'!G15</f>
         <v>-3.0693307053297801E-4</v>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="18">
         <f>'get_proximal_value Validation'!H15</f>
         <v>-9.6095260232686996E-5</v>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="18">
         <f>'get_proximal_value Validation'!I15</f>
         <v>3.5561989992857E-2</v>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="18">
         <f>'get_proximal_value Validation'!J15</f>
         <v>-0.36243444681167603</v>
       </c>
-      <c r="K15" s="28">
+      <c r="K15" s="18">
         <f>'get_proximal_value Validation'!K15</f>
         <v>0.20112581551075001</v>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="18">
         <f>'get_proximal_value Validation'!L15</f>
         <v>5.4567307233810399E-3</v>
       </c>
-      <c r="M15" s="28">
+      <c r="M15" s="18">
         <f>'get_proximal_value Validation'!M15</f>
         <v>0.1</v>
       </c>
-      <c r="N15" s="28">
+      <c r="N15" s="18">
         <v>0.33444876429999998</v>
       </c>
-      <c r="O15" s="28">
+      <c r="O15" s="18">
         <v>0.13783736930000001</v>
       </c>
-      <c r="P15" s="28">
+      <c r="P15" s="18">
         <v>1.5982782000000001E-2</v>
       </c>
-      <c r="Q15" s="28">
+      <c r="Q15" s="18">
         <v>2.3345412470000002</v>
       </c>
-      <c r="R15" s="28">
+      <c r="R15" s="18">
         <v>0.1</v>
       </c>
-      <c r="S15" s="28">
+      <c r="S15" s="18">
         <f t="shared" si="0"/>
         <v>-1.2156425700000029E-2</v>
       </c>
-      <c r="T15" s="28">
+      <c r="T15" s="18">
         <f t="shared" si="1"/>
         <v>7.5497093000000126E-3</v>
       </c>
-      <c r="U15" s="28">
+      <c r="U15" s="18">
         <f t="shared" si="2"/>
         <v>1.5982782000000001E-2</v>
       </c>
-      <c r="V15" s="28">
+      <c r="V15" s="18">
         <f t="shared" si="3"/>
         <v>4.9022770000002325E-3</v>
       </c>
-      <c r="W15" s="39">
+      <c r="W15" s="13">
         <f t="shared" si="4"/>
         <v>2.6498443780298181E-4</v>
       </c>
@@ -8338,66 +8289,66 @@
         <f>'get_proximal_value Validation'!F16</f>
         <v>0</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="18">
         <f>'get_proximal_value Validation'!G16</f>
         <v>1.05677347164601E-3</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="18">
         <f>'get_proximal_value Validation'!H16</f>
         <v>-1.7957310192287001E-3</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="18">
         <f>'get_proximal_value Validation'!I16</f>
         <v>6.4393624663352994E-2</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="18">
         <f>'get_proximal_value Validation'!J16</f>
         <v>-0.26715281605720498</v>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="18">
         <f>'get_proximal_value Validation'!K16</f>
         <v>0.232885867357254</v>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="18">
         <f>'get_proximal_value Validation'!L16</f>
         <v>1.8380418419838E-2</v>
       </c>
-      <c r="M16" s="28">
+      <c r="M16" s="18">
         <f>'get_proximal_value Validation'!M16</f>
         <v>0</v>
       </c>
-      <c r="N16" s="28">
+      <c r="N16" s="18">
         <v>0.3560644027</v>
       </c>
-      <c r="O16" s="28">
+      <c r="O16" s="18">
         <v>0.2</v>
       </c>
-      <c r="P16" s="28">
+      <c r="P16" s="18">
         <v>7.0557252400000006E-2</v>
       </c>
-      <c r="Q16" s="28">
+      <c r="Q16" s="18">
         <v>1.9356272506000001</v>
       </c>
-      <c r="R16" s="28">
-        <v>0</v>
-      </c>
-      <c r="S16" s="28">
+      <c r="R16" s="18">
+        <v>0</v>
+      </c>
+      <c r="S16" s="18">
         <f t="shared" si="0"/>
         <v>-1.5299357299999983E-2</v>
       </c>
-      <c r="T16" s="28">
+      <c r="T16" s="18">
         <f t="shared" si="1"/>
         <v>8.3039599999999991E-3</v>
       </c>
-      <c r="U16" s="28">
+      <c r="U16" s="18">
         <f t="shared" si="2"/>
         <v>7.0557252400000006E-2</v>
       </c>
-      <c r="V16" s="28">
+      <c r="V16" s="18">
         <f t="shared" si="3"/>
         <v>0.22944052060000009</v>
       </c>
-      <c r="W16" s="39">
+      <c r="W16" s="13">
         <f t="shared" si="4"/>
         <v>8.5850392165844003E-2</v>
       </c>
@@ -8427,66 +8378,66 @@
         <f>'get_proximal_value Validation'!F17</f>
         <v>0</v>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="18">
         <f>'get_proximal_value Validation'!G17</f>
         <v>3.5343742929399001E-3</v>
       </c>
-      <c r="H17" s="28">
+      <c r="H17" s="18">
         <f>'get_proximal_value Validation'!H17</f>
         <v>-3.7954235449433301E-3</v>
       </c>
-      <c r="I17" s="28">
+      <c r="I17" s="18">
         <f>'get_proximal_value Validation'!I17</f>
         <v>0.11383625864982599</v>
       </c>
-      <c r="J17" s="28">
+      <c r="J17" s="18">
         <f>'get_proximal_value Validation'!J17</f>
         <v>-0.25536644458770802</v>
       </c>
-      <c r="K17" s="28">
+      <c r="K17" s="18">
         <f>'get_proximal_value Validation'!K17</f>
         <v>0.48884528875351002</v>
       </c>
-      <c r="L17" s="28">
+      <c r="L17" s="18">
         <f>'get_proximal_value Validation'!L17</f>
         <v>2.4793863296508799E-2</v>
       </c>
-      <c r="M17" s="28">
+      <c r="M17" s="18">
         <f>'get_proximal_value Validation'!M17</f>
         <v>0</v>
       </c>
-      <c r="N17" s="28">
+      <c r="N17" s="18">
         <v>0.55320014370000004</v>
       </c>
-      <c r="O17" s="28">
+      <c r="O17" s="18">
         <v>0.2</v>
       </c>
-      <c r="P17" s="28">
+      <c r="P17" s="18">
         <v>4.6837792900000001E-2</v>
       </c>
-      <c r="Q17" s="28">
+      <c r="Q17" s="18">
         <v>1.2222314729999999</v>
       </c>
-      <c r="R17" s="28">
-        <v>0</v>
-      </c>
-      <c r="S17" s="28">
+      <c r="R17" s="18">
+        <v>0</v>
+      </c>
+      <c r="S17" s="18">
         <f t="shared" si="0"/>
         <v>-2.3551396299999916E-2</v>
       </c>
-      <c r="T17" s="28">
+      <c r="T17" s="18">
         <f t="shared" si="1"/>
         <v>5.893300000000018E-3</v>
       </c>
-      <c r="U17" s="28">
+      <c r="U17" s="18">
         <f t="shared" si="2"/>
         <v>4.6837792900000001E-2</v>
       </c>
-      <c r="V17" s="28">
+      <c r="V17" s="18">
         <f t="shared" si="3"/>
         <v>5.0096262999999919E-2</v>
       </c>
-      <c r="W17" s="39">
+      <c r="W17" s="13">
         <f t="shared" si="4"/>
         <v>6.2846777705008365E-3</v>
       </c>
@@ -8516,66 +8467,66 @@
         <f>'get_proximal_value Validation'!F18</f>
         <v>0.99099999999999999</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="18">
         <f>'get_proximal_value Validation'!G18</f>
         <v>-2.8338059782981899E-3</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="18">
         <f>'get_proximal_value Validation'!H18</f>
         <v>-3.8975423667579898E-3</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="18">
         <f>'get_proximal_value Validation'!I18</f>
         <v>-5.2740231156349203E-2</v>
       </c>
-      <c r="J18" s="28">
+      <c r="J18" s="18">
         <f>'get_proximal_value Validation'!J18</f>
         <v>-0.73136901855468806</v>
       </c>
-      <c r="K18" s="28">
+      <c r="K18" s="18">
         <f>'get_proximal_value Validation'!K18</f>
         <v>-0.64403772354125999</v>
       </c>
-      <c r="L18" s="28">
+      <c r="L18" s="18">
         <f>'get_proximal_value Validation'!L18</f>
         <v>3.5194247961044298E-2</v>
       </c>
-      <c r="M18" s="28">
+      <c r="M18" s="18">
         <f>'get_proximal_value Validation'!M18</f>
         <v>0.99099999999999999</v>
       </c>
-      <c r="N18" s="28">
+      <c r="N18" s="18">
         <v>0.63768712449999998</v>
       </c>
-      <c r="O18" s="28">
+      <c r="O18" s="18">
         <v>0.10547438639999999</v>
       </c>
-      <c r="P18" s="28">
+      <c r="P18" s="18">
         <v>4.5002342399999999E-2</v>
       </c>
-      <c r="Q18" s="28">
+      <c r="Q18" s="18">
         <v>-1.5195661146999999</v>
       </c>
-      <c r="R18" s="28">
+      <c r="R18" s="18">
         <v>0.99099999999999999</v>
       </c>
-      <c r="S18" s="28">
+      <c r="S18" s="18">
         <f t="shared" si="0"/>
         <v>-9.3729275499999987E-2</v>
       </c>
-      <c r="T18" s="28">
+      <c r="T18" s="18">
         <f t="shared" si="1"/>
         <v>-1.6522436000000057E-3</v>
       </c>
-      <c r="U18" s="28">
+      <c r="U18" s="18">
         <f t="shared" si="2"/>
         <v>4.5002342399999999E-2</v>
       </c>
-      <c r="V18" s="28">
+      <c r="V18" s="18">
         <f t="shared" si="3"/>
         <v>-0.23492817469999983</v>
       </c>
-      <c r="W18" s="39">
+      <c r="W18" s="13">
         <f t="shared" si="4"/>
         <v>8.1400284762882968E-2</v>
       </c>
@@ -8605,66 +8556,66 @@
         <f>'get_proximal_value Validation'!F19</f>
         <v>0.41199999999999998</v>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="18">
         <f>'get_proximal_value Validation'!G19</f>
         <v>-2.7264871168881698E-3</v>
       </c>
-      <c r="H19" s="28">
+      <c r="H19" s="18">
         <f>'get_proximal_value Validation'!H19</f>
         <v>-2.9036914929747598E-4</v>
       </c>
-      <c r="I19" s="28">
+      <c r="I19" s="18">
         <f>'get_proximal_value Validation'!I19</f>
         <v>6.54015243053436E-2</v>
       </c>
-      <c r="J19" s="28">
+      <c r="J19" s="18">
         <f>'get_proximal_value Validation'!J19</f>
         <v>-0.990095674991608</v>
       </c>
-      <c r="K19" s="28">
+      <c r="K19" s="18">
         <f>'get_proximal_value Validation'!K19</f>
         <v>0.68135464191436801</v>
       </c>
-      <c r="L19" s="28">
+      <c r="L19" s="18">
         <f>'get_proximal_value Validation'!L19</f>
         <v>-9.7361505031585693E-3</v>
       </c>
-      <c r="M19" s="28">
+      <c r="M19" s="18">
         <f>'get_proximal_value Validation'!M19</f>
         <v>0.41199999999999998</v>
       </c>
-      <c r="N19" s="28">
+      <c r="N19" s="18">
         <v>0.90992140170000002</v>
       </c>
-      <c r="O19" s="28">
+      <c r="O19" s="18">
         <v>6.5472843099999997E-2</v>
       </c>
-      <c r="P19" s="28">
+      <c r="P19" s="18">
         <v>-1.47643797E-2</v>
       </c>
-      <c r="Q19" s="28">
+      <c r="Q19" s="18">
         <v>2.1879206054</v>
       </c>
-      <c r="R19" s="28">
+      <c r="R19" s="18">
         <v>0.41199999999999998</v>
       </c>
-      <c r="S19" s="28">
+      <c r="S19" s="18">
         <f t="shared" si="0"/>
         <v>-1.8319078300000013E-2</v>
       </c>
-      <c r="T19" s="28">
+      <c r="T19" s="18">
         <f t="shared" si="1"/>
         <v>3.9738230999999957E-3</v>
       </c>
-      <c r="U19" s="28">
+      <c r="U19" s="18">
         <f t="shared" si="2"/>
         <v>-1.47643797E-2</v>
       </c>
-      <c r="V19" s="28">
+      <c r="V19" s="18">
         <f t="shared" si="3"/>
         <v>-2.5452554600000177E-2</v>
       </c>
-      <c r="W19" s="39">
+      <c r="W19" s="13">
         <f t="shared" si="4"/>
         <v>2.977032523033931E-3</v>
       </c>
@@ -8694,66 +8645,66 @@
         <f>'get_proximal_value Validation'!F20</f>
         <v>1.2649999999999999</v>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="18">
         <f>'get_proximal_value Validation'!G20</f>
         <v>-2.4467429611831899E-3</v>
       </c>
-      <c r="H20" s="28">
+      <c r="H20" s="18">
         <f>'get_proximal_value Validation'!H20</f>
         <v>-3.9606718346476598E-3</v>
       </c>
-      <c r="I20" s="28">
+      <c r="I20" s="18">
         <f>'get_proximal_value Validation'!I20</f>
         <v>-6.55845552682877E-2</v>
       </c>
-      <c r="J20" s="28">
+      <c r="J20" s="18">
         <f>'get_proximal_value Validation'!J20</f>
         <v>-1.3344798088073699</v>
       </c>
-      <c r="K20" s="28">
+      <c r="K20" s="18">
         <f>'get_proximal_value Validation'!K20</f>
         <v>-0.42153304815292397</v>
       </c>
-      <c r="L20" s="28">
+      <c r="L20" s="18">
         <f>'get_proximal_value Validation'!L20</f>
         <v>3.0811607837676998E-2</v>
       </c>
-      <c r="M20" s="28">
+      <c r="M20" s="18">
         <f>'get_proximal_value Validation'!M20</f>
         <v>1.2649999999999999</v>
       </c>
-      <c r="N20" s="28">
+      <c r="N20" s="18">
         <v>0.70956196709999997</v>
       </c>
-      <c r="O20" s="28">
+      <c r="O20" s="18">
         <v>0.18387510060000001</v>
       </c>
-      <c r="P20" s="28">
+      <c r="P20" s="18">
         <v>8.0751721299999996E-2</v>
       </c>
-      <c r="Q20" s="28">
+      <c r="Q20" s="18">
         <v>-2.7659297763000001</v>
       </c>
-      <c r="R20" s="28">
+      <c r="R20" s="18">
         <v>1.2649999999999999</v>
       </c>
-      <c r="S20" s="28">
+      <c r="S20" s="18">
         <f t="shared" si="0"/>
         <v>0.22279014709999995</v>
       </c>
-      <c r="T20" s="28">
+      <c r="T20" s="18">
         <f t="shared" si="1"/>
         <v>-8.7259993999999896E-3</v>
       </c>
-      <c r="U20" s="28">
+      <c r="U20" s="18">
         <f t="shared" si="2"/>
         <v>8.0751721299999996E-2</v>
       </c>
-      <c r="V20" s="28">
+      <c r="V20" s="18">
         <f t="shared" si="3"/>
         <v>-0.79209780630000015</v>
       </c>
-      <c r="W20" s="39">
+      <c r="W20" s="13">
         <f t="shared" si="4"/>
         <v>0.24728932516484134</v>
       </c>
@@ -8783,66 +8734,66 @@
         <f>'get_proximal_value Validation'!F21</f>
         <v>0.28599999999999998</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="18">
         <f>'get_proximal_value Validation'!G21</f>
         <v>-2.2109632845967999E-3</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="18">
         <f>'get_proximal_value Validation'!H21</f>
         <v>-1.3992630410939501E-3</v>
       </c>
-      <c r="I21" s="28">
+      <c r="I21" s="18">
         <f>'get_proximal_value Validation'!I21</f>
         <v>-7.3739819228649098E-2</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="18">
         <f>'get_proximal_value Validation'!J21</f>
         <v>-0.77465367317199696</v>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="18">
         <f>'get_proximal_value Validation'!K21</f>
         <v>-0.54947280883789096</v>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="18">
         <f>'get_proximal_value Validation'!L21</f>
         <v>3.94041240215302E-2</v>
       </c>
-      <c r="M21" s="28">
+      <c r="M21" s="18">
         <f>'get_proximal_value Validation'!M21</f>
         <v>0.28599999999999998</v>
       </c>
-      <c r="N21" s="28">
+      <c r="N21" s="18">
         <v>0.74052383730000004</v>
       </c>
-      <c r="O21" s="28">
+      <c r="O21" s="18">
         <v>0.1244305711</v>
       </c>
-      <c r="P21" s="28">
+      <c r="P21" s="18">
         <v>6.0082425199999998E-2</v>
       </c>
-      <c r="Q21" s="28">
+      <c r="Q21" s="18">
         <v>-2.1140271421999999</v>
       </c>
-      <c r="R21" s="28">
+      <c r="R21" s="18">
         <v>0.28599999999999998</v>
       </c>
-      <c r="S21" s="28">
+      <c r="S21" s="18">
         <f t="shared" si="0"/>
         <v>-1.9324612699999966E-2</v>
       </c>
-      <c r="T21" s="28">
+      <c r="T21" s="18">
         <f t="shared" si="1"/>
         <v>1.2077361100000003E-2</v>
       </c>
-      <c r="U21" s="28">
+      <c r="U21" s="18">
         <f t="shared" si="2"/>
         <v>6.0082425199999998E-2</v>
       </c>
-      <c r="V21" s="28">
+      <c r="V21" s="18">
         <f t="shared" si="3"/>
         <v>-5.2457972200000036E-2</v>
       </c>
-      <c r="W21" s="39">
+      <c r="W21" s="13">
         <f t="shared" si="4"/>
         <v>1.4228089616195926E-7</v>
       </c>
@@ -8872,66 +8823,66 @@
         <f>'get_proximal_value Validation'!F22</f>
         <v>0.125</v>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="18">
         <f>'get_proximal_value Validation'!G22</f>
         <v>-5.2654783939942696E-4</v>
       </c>
-      <c r="H22" s="28">
+      <c r="H22" s="18">
         <f>'get_proximal_value Validation'!H22</f>
         <v>-6.8196270149201198E-4</v>
       </c>
-      <c r="I22" s="28">
+      <c r="I22" s="18">
         <f>'get_proximal_value Validation'!I22</f>
         <v>-7.9568028450012207E-3</v>
       </c>
-      <c r="J22" s="28">
+      <c r="J22" s="18">
         <f>'get_proximal_value Validation'!J22</f>
         <v>-0.14130574464797999</v>
       </c>
-      <c r="K22" s="28">
+      <c r="K22" s="18">
         <f>'get_proximal_value Validation'!K22</f>
         <v>-5.4839767515659298E-2</v>
       </c>
-      <c r="L22" s="28">
+      <c r="L22" s="18">
         <f>'get_proximal_value Validation'!L22</f>
         <v>1.5218697488308E-2</v>
       </c>
-      <c r="M22" s="28">
+      <c r="M22" s="18">
         <f>'get_proximal_value Validation'!M22</f>
         <v>0.125</v>
       </c>
-      <c r="N22" s="28">
+      <c r="N22" s="18">
         <v>6.2152555300000002E-2</v>
       </c>
-      <c r="O22" s="28">
+      <c r="O22" s="18">
         <v>0.18302933900000001</v>
       </c>
-      <c r="P22" s="28">
+      <c r="P22" s="18">
         <v>0.2338209819</v>
       </c>
-      <c r="Q22" s="28">
+      <c r="Q22" s="18">
         <v>-2.0309694221000001</v>
       </c>
-      <c r="R22" s="28">
+      <c r="R22" s="18">
         <v>0.125</v>
       </c>
-      <c r="S22" s="28">
+      <c r="S22" s="18">
         <f t="shared" si="0"/>
         <v>1.7524753000000004E-3</v>
       </c>
-      <c r="T22" s="28">
+      <c r="T22" s="18">
         <f t="shared" si="1"/>
         <v>3.0368490000000081E-3</v>
       </c>
-      <c r="U22" s="28">
+      <c r="U22" s="18">
         <f t="shared" si="2"/>
         <v>0.2338209819</v>
       </c>
-      <c r="V22" s="28">
+      <c r="V22" s="18">
         <f t="shared" si="3"/>
         <v>0.16953835790000005</v>
       </c>
-      <c r="W22" s="39">
+      <c r="W22" s="13">
         <f t="shared" si="4"/>
         <v>0.16658533200661468</v>
       </c>
@@ -8961,66 +8912,66 @@
         <f>'get_proximal_value Validation'!F23</f>
         <v>0.53900000000000003</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="18">
         <f>'get_proximal_value Validation'!G23</f>
         <v>-1.2194762239232701E-3</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="18">
         <f>'get_proximal_value Validation'!H23</f>
         <v>-1.72514526639134E-3</v>
       </c>
-      <c r="I23" s="28">
+      <c r="I23" s="18">
         <f>'get_proximal_value Validation'!I23</f>
         <v>-1.7789617180824301E-2</v>
       </c>
-      <c r="J23" s="28">
+      <c r="J23" s="18">
         <f>'get_proximal_value Validation'!J23</f>
         <v>-0.53096002340316795</v>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="18">
         <f>'get_proximal_value Validation'!K23</f>
         <v>-0.15755756199359899</v>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="18">
         <f>'get_proximal_value Validation'!L23</f>
         <v>1.7692722380161299E-2</v>
       </c>
-      <c r="M23" s="28">
+      <c r="M23" s="18">
         <f>'get_proximal_value Validation'!M23</f>
         <v>0.53900000000000003</v>
       </c>
-      <c r="N23" s="28">
+      <c r="N23" s="18">
         <v>0.1540387838</v>
       </c>
-      <c r="O23" s="28">
+      <c r="O23" s="18">
         <v>0.2</v>
       </c>
-      <c r="P23" s="28">
+      <c r="P23" s="18">
         <v>8.8658265E-2</v>
       </c>
-      <c r="Q23" s="28">
+      <c r="Q23" s="18">
         <v>-1.8345180439</v>
       </c>
-      <c r="R23" s="28">
+      <c r="R23" s="18">
         <v>0.53900000000000003</v>
       </c>
-      <c r="S23" s="28">
+      <c r="S23" s="18">
         <f t="shared" si="0"/>
         <v>-1.9568466199999995E-2</v>
       </c>
-      <c r="T23" s="28">
+      <c r="T23" s="18">
         <f t="shared" si="1"/>
         <v>2.4000100000000024E-2</v>
       </c>
-      <c r="U23" s="28">
+      <c r="U23" s="18">
         <f t="shared" si="2"/>
         <v>8.8658265E-2</v>
       </c>
-      <c r="V23" s="28">
+      <c r="V23" s="18">
         <f t="shared" si="3"/>
         <v>-0.10712537389999999</v>
       </c>
-      <c r="W23" s="39">
+      <c r="W23" s="13">
         <f t="shared" si="4"/>
         <v>1.9699456128271885E-4</v>
       </c>
@@ -9050,23 +9001,23 @@
         <f>'get_proximal_value Validation'!F24</f>
         <v>0</v>
       </c>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="28"/>
-      <c r="N24" s="29"/>
-      <c r="O24" s="29"/>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="29"/>
-      <c r="S24" s="28"/>
-      <c r="T24" s="28"/>
-      <c r="U24" s="28"/>
-      <c r="V24" s="28"/>
-      <c r="W24" s="39"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="18"/>
+      <c r="T24" s="18"/>
+      <c r="U24" s="18"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="13"/>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -9093,23 +9044,23 @@
         <f>'get_proximal_value Validation'!F25</f>
         <v>0</v>
       </c>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="29"/>
-      <c r="O25" s="29"/>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="29"/>
-      <c r="R25" s="29"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="28"/>
-      <c r="U25" s="28"/>
-      <c r="V25" s="28"/>
-      <c r="W25" s="39"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="18"/>
+      <c r="T25" s="18"/>
+      <c r="U25" s="18"/>
+      <c r="V25" s="18"/>
+      <c r="W25" s="13"/>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -9136,23 +9087,23 @@
         <f>'get_proximal_value Validation'!F26</f>
         <v>0</v>
       </c>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="28"/>
-      <c r="U26" s="28"/>
-      <c r="V26" s="28"/>
-      <c r="W26" s="39"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="18"/>
+      <c r="T26" s="18"/>
+      <c r="U26" s="18"/>
+      <c r="V26" s="18"/>
+      <c r="W26" s="13"/>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
@@ -9179,23 +9130,23 @@
         <f>'get_proximal_value Validation'!F27</f>
         <v>0</v>
       </c>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="29"/>
-      <c r="O27" s="29"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="29"/>
-      <c r="R27" s="29"/>
-      <c r="S27" s="28"/>
-      <c r="T27" s="28"/>
-      <c r="U27" s="28"/>
-      <c r="V27" s="28"/>
-      <c r="W27" s="39"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="18"/>
+      <c r="T27" s="18"/>
+      <c r="U27" s="18"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="13"/>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
@@ -9222,23 +9173,23 @@
         <f>'get_proximal_value Validation'!F28</f>
         <v>0</v>
       </c>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="29"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="28"/>
-      <c r="T28" s="28"/>
-      <c r="U28" s="28"/>
-      <c r="V28" s="28"/>
-      <c r="W28" s="39"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="18"/>
+      <c r="T28" s="18"/>
+      <c r="U28" s="18"/>
+      <c r="V28" s="18"/>
+      <c r="W28" s="13"/>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
@@ -9265,23 +9216,23 @@
         <f>'get_proximal_value Validation'!F29</f>
         <v>0</v>
       </c>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
-      <c r="U29" s="28"/>
-      <c r="V29" s="28"/>
-      <c r="W29" s="39"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="18"/>
+      <c r="U29" s="18"/>
+      <c r="V29" s="18"/>
+      <c r="W29" s="13"/>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
@@ -9308,23 +9259,23 @@
         <f>'get_proximal_value Validation'!F30</f>
         <v>0</v>
       </c>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
-      <c r="M30" s="28"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="29"/>
-      <c r="P30" s="29"/>
-      <c r="Q30" s="29"/>
-      <c r="R30" s="29"/>
-      <c r="S30" s="28"/>
-      <c r="T30" s="28"/>
-      <c r="U30" s="28"/>
-      <c r="V30" s="28"/>
-      <c r="W30" s="39"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="18"/>
+      <c r="T30" s="18"/>
+      <c r="U30" s="18"/>
+      <c r="V30" s="18"/>
+      <c r="W30" s="13"/>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
@@ -9351,23 +9302,23 @@
         <f>'get_proximal_value Validation'!F31</f>
         <v>0</v>
       </c>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="28"/>
-      <c r="N31" s="29"/>
-      <c r="O31" s="29"/>
-      <c r="P31" s="29"/>
-      <c r="Q31" s="29"/>
-      <c r="R31" s="29"/>
-      <c r="S31" s="28"/>
-      <c r="T31" s="28"/>
-      <c r="U31" s="28"/>
-      <c r="V31" s="28"/>
-      <c r="W31" s="39"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="19"/>
+      <c r="S31" s="18"/>
+      <c r="T31" s="18"/>
+      <c r="U31" s="18"/>
+      <c r="V31" s="18"/>
+      <c r="W31" s="13"/>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
@@ -9394,23 +9345,23 @@
         <f>'get_proximal_value Validation'!F32</f>
         <v>0</v>
       </c>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="39"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="19"/>
+      <c r="S32" s="18"/>
+      <c r="T32" s="18"/>
+      <c r="U32" s="18"/>
+      <c r="V32" s="18"/>
+      <c r="W32" s="13"/>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
@@ -9437,23 +9388,23 @@
         <f>'get_proximal_value Validation'!F33</f>
         <v>0</v>
       </c>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
-      <c r="M33" s="28"/>
-      <c r="N33" s="29"/>
-      <c r="O33" s="29"/>
-      <c r="P33" s="29"/>
-      <c r="Q33" s="29"/>
-      <c r="R33" s="29"/>
-      <c r="S33" s="28"/>
-      <c r="T33" s="28"/>
-      <c r="U33" s="28"/>
-      <c r="V33" s="28"/>
-      <c r="W33" s="39"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="19"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="18"/>
+      <c r="U33" s="18"/>
+      <c r="V33" s="18"/>
+      <c r="W33" s="13"/>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
@@ -9480,23 +9431,23 @@
         <f>'get_proximal_value Validation'!F34</f>
         <v>0</v>
       </c>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="28"/>
-      <c r="N34" s="28"/>
-      <c r="O34" s="28"/>
-      <c r="P34" s="28"/>
-      <c r="Q34" s="28"/>
-      <c r="R34" s="28"/>
-      <c r="S34" s="28"/>
-      <c r="T34" s="28"/>
-      <c r="U34" s="28"/>
-      <c r="V34" s="28"/>
-      <c r="W34" s="39"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="18"/>
+      <c r="Q34" s="18"/>
+      <c r="R34" s="18"/>
+      <c r="S34" s="18"/>
+      <c r="T34" s="18"/>
+      <c r="U34" s="18"/>
+      <c r="V34" s="18"/>
+      <c r="W34" s="13"/>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
@@ -9523,23 +9474,23 @@
         <f>'get_proximal_value Validation'!F35</f>
         <v>0</v>
       </c>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28"/>
-      <c r="N35" s="28"/>
-      <c r="O35" s="28"/>
-      <c r="P35" s="28"/>
-      <c r="Q35" s="28"/>
-      <c r="R35" s="28"/>
-      <c r="S35" s="28"/>
-      <c r="T35" s="28"/>
-      <c r="U35" s="28"/>
-      <c r="V35" s="28"/>
-      <c r="W35" s="39"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="18"/>
+      <c r="R35" s="18"/>
+      <c r="S35" s="18"/>
+      <c r="T35" s="18"/>
+      <c r="U35" s="18"/>
+      <c r="V35" s="18"/>
+      <c r="W35" s="13"/>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
@@ -9566,23 +9517,23 @@
         <f>'get_proximal_value Validation'!F36</f>
         <v>0</v>
       </c>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="28"/>
-      <c r="N36" s="28"/>
-      <c r="O36" s="28"/>
-      <c r="P36" s="28"/>
-      <c r="Q36" s="28"/>
-      <c r="R36" s="28"/>
-      <c r="S36" s="28"/>
-      <c r="T36" s="28"/>
-      <c r="U36" s="28"/>
-      <c r="V36" s="28"/>
-      <c r="W36" s="39"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="18"/>
+      <c r="Q36" s="18"/>
+      <c r="R36" s="18"/>
+      <c r="S36" s="18"/>
+      <c r="T36" s="18"/>
+      <c r="U36" s="18"/>
+      <c r="V36" s="18"/>
+      <c r="W36" s="13"/>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
@@ -9609,23 +9560,23 @@
         <f>'get_proximal_value Validation'!F37</f>
         <v>0</v>
       </c>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
-      <c r="U37" s="28"/>
-      <c r="V37" s="28"/>
-      <c r="W37" s="39"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="18"/>
+      <c r="R37" s="18"/>
+      <c r="S37" s="18"/>
+      <c r="T37" s="18"/>
+      <c r="U37" s="18"/>
+      <c r="V37" s="18"/>
+      <c r="W37" s="13"/>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -9652,23 +9603,23 @@
         <f>'get_proximal_value Validation'!F38</f>
         <v>0</v>
       </c>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="28"/>
-      <c r="N38" s="28"/>
-      <c r="O38" s="28"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="28"/>
-      <c r="R38" s="28"/>
-      <c r="S38" s="28"/>
-      <c r="T38" s="28"/>
-      <c r="U38" s="28"/>
-      <c r="V38" s="28"/>
-      <c r="W38" s="39"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="18"/>
+      <c r="S38" s="18"/>
+      <c r="T38" s="18"/>
+      <c r="U38" s="18"/>
+      <c r="V38" s="18"/>
+      <c r="W38" s="13"/>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -9695,23 +9646,23 @@
         <f>'get_proximal_value Validation'!F39</f>
         <v>0</v>
       </c>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="28"/>
-      <c r="N39" s="28"/>
-      <c r="O39" s="28"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="28"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="28"/>
-      <c r="T39" s="28"/>
-      <c r="U39" s="28"/>
-      <c r="V39" s="28"/>
-      <c r="W39" s="39"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="18"/>
+      <c r="Q39" s="18"/>
+      <c r="R39" s="18"/>
+      <c r="S39" s="18"/>
+      <c r="T39" s="18"/>
+      <c r="U39" s="18"/>
+      <c r="V39" s="18"/>
+      <c r="W39" s="13"/>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
@@ -9738,23 +9689,23 @@
         <f>'get_proximal_value Validation'!F40</f>
         <v>0</v>
       </c>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28"/>
-      <c r="T40" s="28"/>
-      <c r="U40" s="28"/>
-      <c r="V40" s="28"/>
-      <c r="W40" s="39"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="18"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="18"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="18"/>
+      <c r="V40" s="18"/>
+      <c r="W40" s="13"/>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
@@ -9763,22 +9714,22 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="28"/>
-      <c r="N41" s="29"/>
-      <c r="O41" s="29"/>
-      <c r="P41" s="29"/>
-      <c r="Q41" s="29"/>
-      <c r="R41" s="29"/>
-      <c r="S41" s="29"/>
-      <c r="T41" s="29"/>
-      <c r="U41" s="29"/>
-      <c r="V41" s="29"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+      <c r="N41" s="19"/>
+      <c r="O41" s="19"/>
+      <c r="P41" s="19"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="19"/>
+      <c r="S41" s="19"/>
+      <c r="T41" s="19"/>
+      <c r="U41" s="19"/>
+      <c r="V41" s="19"/>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
@@ -9787,464 +9738,491 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
-      <c r="K42" s="28"/>
-      <c r="L42" s="28"/>
-      <c r="M42" s="28"/>
-      <c r="N42" s="29"/>
-      <c r="O42" s="29"/>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="29"/>
-      <c r="R42" s="29"/>
-      <c r="S42" s="29"/>
-      <c r="T42" s="29"/>
-      <c r="U42" s="29"/>
-      <c r="V42" s="29"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="18"/>
+      <c r="N42" s="19"/>
+      <c r="O42" s="19"/>
+      <c r="P42" s="19"/>
+      <c r="Q42" s="19"/>
+      <c r="R42" s="19"/>
+      <c r="S42" s="19"/>
+      <c r="T42" s="19"/>
+      <c r="U42" s="19"/>
+      <c r="V42" s="19"/>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A43" s="29"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
+      <c r="A43" s="19"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18"/>
+      <c r="N43" s="19"/>
+      <c r="O43" s="19"/>
+      <c r="P43" s="19"/>
+      <c r="Q43" s="19"/>
+      <c r="R43" s="19"/>
+      <c r="S43" s="19"/>
+      <c r="T43" s="19"/>
+      <c r="U43" s="19"/>
+      <c r="V43" s="19"/>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A44" s="29"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="28"/>
-      <c r="M44" s="28"/>
-      <c r="N44" s="29"/>
-      <c r="O44" s="29"/>
-      <c r="P44" s="29"/>
-      <c r="Q44" s="29"/>
-      <c r="R44" s="29"/>
-      <c r="S44" s="29"/>
-      <c r="T44" s="29"/>
-      <c r="U44" s="29"/>
-      <c r="V44" s="29"/>
+      <c r="A44" s="19"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+      <c r="N44" s="19"/>
+      <c r="O44" s="19"/>
+      <c r="P44" s="19"/>
+      <c r="Q44" s="19"/>
+      <c r="R44" s="19"/>
+      <c r="S44" s="19"/>
+      <c r="T44" s="19"/>
+      <c r="U44" s="19"/>
+      <c r="V44" s="19"/>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A45" s="29"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="28"/>
-      <c r="M45" s="28"/>
-      <c r="N45" s="29"/>
-      <c r="O45" s="29"/>
-      <c r="P45" s="29"/>
-      <c r="Q45" s="29"/>
-      <c r="R45" s="29"/>
-      <c r="S45" s="29"/>
-      <c r="T45" s="29"/>
-      <c r="U45" s="29"/>
-      <c r="V45" s="29"/>
+      <c r="A45" s="19"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="19"/>
+      <c r="O45" s="19"/>
+      <c r="P45" s="19"/>
+      <c r="Q45" s="19"/>
+      <c r="R45" s="19"/>
+      <c r="S45" s="19"/>
+      <c r="T45" s="19"/>
+      <c r="U45" s="19"/>
+      <c r="V45" s="19"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A46" s="29"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="28"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
+      <c r="A46" s="19"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18"/>
+      <c r="N46" s="19"/>
+      <c r="O46" s="19"/>
+      <c r="P46" s="19"/>
+      <c r="Q46" s="19"/>
+      <c r="R46" s="19"/>
+      <c r="S46" s="19"/>
+      <c r="T46" s="19"/>
+      <c r="U46" s="19"/>
+      <c r="V46" s="19"/>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A47" s="29">
+      <c r="A47" s="19">
         <f>'get_proximal_value Validation'!A47</f>
         <v>0</v>
       </c>
-      <c r="B47" s="29">
+      <c r="B47" s="19">
         <f>'get_proximal_value Validation'!B47</f>
         <v>0</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="19">
         <f>'get_proximal_value Validation'!C47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="29">
+      <c r="D47" s="19">
         <f>'get_proximal_value Validation'!D47</f>
         <v>0</v>
       </c>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29">
+      <c r="E47" s="19"/>
+      <c r="F47" s="19">
         <f>'get_proximal_value Validation'!F47</f>
         <v>0</v>
       </c>
-      <c r="G47" s="29">
-        <v>0</v>
-      </c>
-      <c r="H47" s="29">
-        <v>0</v>
-      </c>
-      <c r="I47" s="29">
-        <v>0</v>
-      </c>
-      <c r="J47" s="29">
-        <v>0</v>
-      </c>
-      <c r="K47" s="29">
-        <v>0</v>
-      </c>
-      <c r="L47" s="29">
-        <v>0</v>
-      </c>
-      <c r="M47" s="29"/>
-      <c r="N47" s="29"/>
-      <c r="O47" s="29"/>
-      <c r="P47" s="29"/>
-      <c r="Q47" s="29"/>
-      <c r="R47" s="29"/>
-      <c r="S47" s="29"/>
-      <c r="T47" s="29"/>
-      <c r="U47" s="29"/>
-      <c r="V47" s="29"/>
+      <c r="G47" s="19">
+        <v>0</v>
+      </c>
+      <c r="H47" s="19">
+        <v>0</v>
+      </c>
+      <c r="I47" s="19">
+        <v>0</v>
+      </c>
+      <c r="J47" s="19">
+        <v>0</v>
+      </c>
+      <c r="K47" s="19">
+        <v>0</v>
+      </c>
+      <c r="L47" s="19">
+        <v>0</v>
+      </c>
+      <c r="M47" s="19"/>
+      <c r="N47" s="19"/>
+      <c r="O47" s="19"/>
+      <c r="P47" s="19"/>
+      <c r="Q47" s="19"/>
+      <c r="R47" s="19"/>
+      <c r="S47" s="19"/>
+      <c r="T47" s="19"/>
+      <c r="U47" s="19"/>
+      <c r="V47" s="19"/>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="29">
+      <c r="A48" s="19">
         <f>'get_proximal_value Validation'!A48</f>
         <v>0</v>
       </c>
-      <c r="B48" s="29">
+      <c r="B48" s="19">
         <f>'get_proximal_value Validation'!B48</f>
         <v>0</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="19">
         <f>'get_proximal_value Validation'!C48</f>
         <v>0</v>
       </c>
-      <c r="D48" s="29">
+      <c r="D48" s="19">
         <f>'get_proximal_value Validation'!D48</f>
         <v>0</v>
       </c>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29">
+      <c r="E48" s="19"/>
+      <c r="F48" s="19">
         <f>'get_proximal_value Validation'!F48</f>
         <v>0</v>
       </c>
-      <c r="G48" s="29">
-        <v>0</v>
-      </c>
-      <c r="H48" s="29">
-        <v>0</v>
-      </c>
-      <c r="I48" s="29">
-        <v>0</v>
-      </c>
-      <c r="J48" s="29">
-        <v>0</v>
-      </c>
-      <c r="K48" s="29">
-        <v>0</v>
-      </c>
-      <c r="L48" s="29">
-        <v>0</v>
-      </c>
-      <c r="M48" s="29"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="29"/>
-      <c r="S48" s="29"/>
-      <c r="T48" s="29"/>
-      <c r="U48" s="29"/>
-      <c r="V48" s="29"/>
+      <c r="G48" s="19">
+        <v>0</v>
+      </c>
+      <c r="H48" s="19">
+        <v>0</v>
+      </c>
+      <c r="I48" s="19">
+        <v>0</v>
+      </c>
+      <c r="J48" s="19">
+        <v>0</v>
+      </c>
+      <c r="K48" s="19">
+        <v>0</v>
+      </c>
+      <c r="L48" s="19">
+        <v>0</v>
+      </c>
+      <c r="M48" s="19"/>
+      <c r="N48" s="19"/>
+      <c r="O48" s="19"/>
+      <c r="P48" s="19"/>
+      <c r="Q48" s="19"/>
+      <c r="R48" s="19"/>
+      <c r="S48" s="19"/>
+      <c r="T48" s="19"/>
+      <c r="U48" s="19"/>
+      <c r="V48" s="19"/>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A49" s="29">
+      <c r="A49" s="19">
         <f>'get_proximal_value Validation'!A49</f>
         <v>0</v>
       </c>
-      <c r="B49" s="29">
+      <c r="B49" s="19">
         <f>'get_proximal_value Validation'!B49</f>
         <v>0</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="19">
         <f>'get_proximal_value Validation'!C49</f>
         <v>0</v>
       </c>
-      <c r="D49" s="29">
+      <c r="D49" s="19">
         <f>'get_proximal_value Validation'!D49</f>
         <v>0</v>
       </c>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29">
+      <c r="E49" s="19"/>
+      <c r="F49" s="19">
         <f>'get_proximal_value Validation'!F49</f>
         <v>0</v>
       </c>
-      <c r="G49" s="40">
-        <v>0</v>
-      </c>
-      <c r="H49" s="29">
-        <v>0</v>
-      </c>
-      <c r="I49" s="29">
-        <v>0</v>
-      </c>
-      <c r="J49" s="29">
-        <v>0</v>
-      </c>
-      <c r="K49" s="29">
-        <v>0</v>
-      </c>
-      <c r="L49" s="29">
-        <v>0</v>
-      </c>
-      <c r="M49" s="41"/>
-      <c r="N49" s="42"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="29"/>
-      <c r="R49" s="29"/>
-      <c r="S49" s="43" t="s">
+      <c r="G49" s="20">
+        <v>0</v>
+      </c>
+      <c r="H49" s="19">
+        <v>0</v>
+      </c>
+      <c r="I49" s="19">
+        <v>0</v>
+      </c>
+      <c r="J49" s="19">
+        <v>0</v>
+      </c>
+      <c r="K49" s="19">
+        <v>0</v>
+      </c>
+      <c r="L49" s="19">
+        <v>0</v>
+      </c>
+      <c r="M49" s="21"/>
+      <c r="N49" s="22"/>
+      <c r="O49" s="19"/>
+      <c r="P49" s="19"/>
+      <c r="Q49" s="19"/>
+      <c r="R49" s="19"/>
+      <c r="S49" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="T49" s="43"/>
-      <c r="U49" s="43"/>
-      <c r="V49" s="43"/>
+      <c r="T49" s="37"/>
+      <c r="U49" s="37"/>
+      <c r="V49" s="37"/>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A50" s="29">
+      <c r="A50" s="19">
         <f>'get_proximal_value Validation'!A50</f>
         <v>0</v>
       </c>
-      <c r="B50" s="29">
+      <c r="B50" s="19">
         <f>'get_proximal_value Validation'!B50</f>
         <v>0</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="19">
         <f>'get_proximal_value Validation'!C50</f>
         <v>0</v>
       </c>
-      <c r="D50" s="29">
+      <c r="D50" s="19">
         <f>'get_proximal_value Validation'!D50</f>
         <v>0</v>
       </c>
-      <c r="E50" s="29"/>
-      <c r="F50" s="29">
+      <c r="E50" s="19"/>
+      <c r="F50" s="19">
         <f>'get_proximal_value Validation'!F50</f>
         <v>0</v>
       </c>
-      <c r="G50" s="40">
-        <v>0</v>
-      </c>
-      <c r="H50" s="29">
-        <v>0</v>
-      </c>
-      <c r="I50" s="29">
-        <v>0</v>
-      </c>
-      <c r="J50" s="29">
-        <v>0</v>
-      </c>
-      <c r="K50" s="29">
-        <v>0</v>
-      </c>
-      <c r="L50" s="29">
-        <v>0</v>
-      </c>
-      <c r="M50" s="41"/>
-      <c r="N50" s="42"/>
-      <c r="O50" s="29"/>
-      <c r="P50" s="29"/>
-      <c r="Q50" s="29"/>
-      <c r="R50" s="29"/>
-      <c r="S50" s="29">
+      <c r="G50" s="20">
+        <v>0</v>
+      </c>
+      <c r="H50" s="19">
+        <v>0</v>
+      </c>
+      <c r="I50" s="19">
+        <v>0</v>
+      </c>
+      <c r="J50" s="19">
+        <v>0</v>
+      </c>
+      <c r="K50" s="19">
+        <v>0</v>
+      </c>
+      <c r="L50" s="19">
+        <v>0</v>
+      </c>
+      <c r="M50" s="21"/>
+      <c r="N50" s="22"/>
+      <c r="O50" s="19"/>
+      <c r="P50" s="19"/>
+      <c r="Q50" s="19"/>
+      <c r="R50" s="19"/>
+      <c r="S50" s="19">
         <f>AVERAGE(S4:S48)</f>
         <v>-9.6472597149999985E-3</v>
       </c>
-      <c r="T50" s="29">
+      <c r="T50" s="19">
         <f t="shared" ref="T50:V50" si="5">AVERAGE(T4:T48)</f>
         <v>7.5463757750000044E-3</v>
       </c>
-      <c r="U50" s="29">
+      <c r="U50" s="19">
         <f t="shared" si="5"/>
         <v>6.5529937990000009E-2</v>
       </c>
-      <c r="V50" s="29">
+      <c r="V50" s="19">
         <f t="shared" si="5"/>
         <v>-6.0887704434999967E-2</v>
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A51" s="29">
+      <c r="A51" s="19">
         <f>'get_proximal_value Validation'!A51</f>
         <v>0</v>
       </c>
-      <c r="B51" s="29">
+      <c r="B51" s="19">
         <f>'get_proximal_value Validation'!B51</f>
         <v>0</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="19">
         <f>'get_proximal_value Validation'!C51</f>
         <v>0</v>
       </c>
-      <c r="D51" s="29">
+      <c r="D51" s="19">
         <f>'get_proximal_value Validation'!D51</f>
         <v>0</v>
       </c>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29">
+      <c r="E51" s="19"/>
+      <c r="F51" s="19">
         <f>'get_proximal_value Validation'!F51</f>
         <v>0</v>
       </c>
-      <c r="G51" s="40">
-        <v>0</v>
-      </c>
-      <c r="H51" s="29">
-        <v>0</v>
-      </c>
-      <c r="I51" s="29">
-        <v>0</v>
-      </c>
-      <c r="J51" s="29">
-        <v>0</v>
-      </c>
-      <c r="K51" s="29">
-        <v>0</v>
-      </c>
-      <c r="L51" s="29">
-        <v>0</v>
-      </c>
-      <c r="M51" s="41"/>
-      <c r="N51" s="42"/>
-      <c r="O51" s="29"/>
-      <c r="P51" s="29"/>
-      <c r="Q51" s="29"/>
-      <c r="R51" s="29"/>
-      <c r="S51" s="43" t="s">
+      <c r="G51" s="20">
+        <v>0</v>
+      </c>
+      <c r="H51" s="19">
+        <v>0</v>
+      </c>
+      <c r="I51" s="19">
+        <v>0</v>
+      </c>
+      <c r="J51" s="19">
+        <v>0</v>
+      </c>
+      <c r="K51" s="19">
+        <v>0</v>
+      </c>
+      <c r="L51" s="19">
+        <v>0</v>
+      </c>
+      <c r="M51" s="21"/>
+      <c r="N51" s="22"/>
+      <c r="O51" s="19"/>
+      <c r="P51" s="19"/>
+      <c r="Q51" s="19"/>
+      <c r="R51" s="19"/>
+      <c r="S51" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="T51" s="43"/>
-      <c r="U51" s="43"/>
-      <c r="V51" s="43"/>
+      <c r="T51" s="37"/>
+      <c r="U51" s="37"/>
+      <c r="V51" s="37"/>
     </row>
     <row r="52" spans="1:22" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="29">
+      <c r="A52" s="19">
         <f>'get_proximal_value Validation'!A52</f>
         <v>0</v>
       </c>
-      <c r="B52" s="29">
+      <c r="B52" s="19">
         <f>'get_proximal_value Validation'!B52</f>
         <v>0</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C52" s="19">
         <f>'get_proximal_value Validation'!C52</f>
         <v>0</v>
       </c>
-      <c r="D52" s="29">
+      <c r="D52" s="19">
         <f>'get_proximal_value Validation'!D52</f>
         <v>0</v>
       </c>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29">
+      <c r="E52" s="19"/>
+      <c r="F52" s="19">
         <f>'get_proximal_value Validation'!F52</f>
         <v>0</v>
       </c>
-      <c r="G52" s="44">
-        <v>0</v>
-      </c>
-      <c r="H52" s="45">
-        <v>0</v>
-      </c>
-      <c r="I52" s="45">
-        <v>0</v>
-      </c>
-      <c r="J52" s="45">
-        <v>0</v>
-      </c>
-      <c r="K52" s="45">
-        <v>0</v>
-      </c>
-      <c r="L52" s="45">
-        <v>0</v>
-      </c>
-      <c r="M52" s="46"/>
-      <c r="N52" s="47"/>
-      <c r="O52" s="45"/>
-      <c r="P52" s="45"/>
-      <c r="Q52" s="45"/>
-      <c r="R52" s="29"/>
-      <c r="S52" s="29">
+      <c r="G52" s="23">
+        <v>0</v>
+      </c>
+      <c r="H52" s="24">
+        <v>0</v>
+      </c>
+      <c r="I52" s="24">
+        <v>0</v>
+      </c>
+      <c r="J52" s="24">
+        <v>0</v>
+      </c>
+      <c r="K52" s="24">
+        <v>0</v>
+      </c>
+      <c r="L52" s="24">
+        <v>0</v>
+      </c>
+      <c r="M52" s="25"/>
+      <c r="N52" s="26"/>
+      <c r="O52" s="24"/>
+      <c r="P52" s="24"/>
+      <c r="Q52" s="24"/>
+      <c r="R52" s="19"/>
+      <c r="S52" s="19">
         <f>_xlfn.STDEV.S(S4:S48)</f>
         <v>6.0123298368721219E-2</v>
       </c>
-      <c r="T52" s="29">
+      <c r="T52" s="19">
         <f t="shared" ref="T52:V52" si="6">_xlfn.STDEV.S(T4:T48)</f>
         <v>8.1254760996205665E-3</v>
       </c>
-      <c r="U52" s="29">
+      <c r="U52" s="19">
         <f t="shared" si="6"/>
         <v>5.1543813020579879E-2</v>
       </c>
-      <c r="V52" s="29">
+      <c r="V52" s="19">
         <f t="shared" si="6"/>
         <v>0.21212942173553898</v>
       </c>
     </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="S53" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="T53" s="37"/>
+      <c r="U53" s="37"/>
+      <c r="V53" s="37"/>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="S54" s="3" cm="1">
+        <f t="array" ref="S54">AVERAGE(ABS(S4:S23))</f>
+        <v>3.532043885499999E-2</v>
+      </c>
+      <c r="T54" s="3" cm="1">
+        <f t="array" ref="T54">AVERAGE(ABS(T4:T23))</f>
+        <v>8.6512730250000031E-3</v>
+      </c>
+      <c r="U54" s="3" cm="1">
+        <f t="array" ref="U54">AVERAGE(ABS(U4:U23))</f>
+        <v>6.7006375960000003E-2</v>
+      </c>
+      <c r="V54" s="3" cm="1">
+        <f t="array" ref="V54">AVERAGE(ABS(V4:V23))</f>
+        <v>0.13233102132500005</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="Z2:AE2"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="S53:V53"/>
     <mergeCell ref="S49:V49"/>
     <mergeCell ref="S51:V51"/>
     <mergeCell ref="G2:M2"/>
     <mergeCell ref="N2:R2"/>
     <mergeCell ref="S2:V2"/>
-    <mergeCell ref="Z2:AE2"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:V1"/>
-    <mergeCell ref="W2:W3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -10506,20 +10484,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10542,14 +10520,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -10564,4 +10534,12 @@
     <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>